--- a/results/Treatment_1974/synth_results_1974.xlsx
+++ b/results/Treatment_1974/synth_results_1974.xlsx
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -391,16 +391,16 @@
         <v>1950</v>
       </c>
       <c r="B2">
-        <v>0.0008904109589041096</v>
+        <v>0.0008925109307836388</v>
       </c>
       <c r="C2">
-        <v>0.0009244388279814115</v>
+        <v>0.0009205595947447368</v>
       </c>
       <c r="D2">
-        <v>-3.402786907730194E-05</v>
+        <v>-2.804866396109804E-05</v>
       </c>
       <c r="E2">
-        <v>-3.680921662670163</v>
+        <v>-3.046914520387536</v>
       </c>
     </row>
     <row r="3">
@@ -408,16 +408,16 @@
         <v>1951</v>
       </c>
       <c r="B3">
-        <v>0.0005999999999999999</v>
+        <v>0.000601264402394389</v>
       </c>
       <c r="C3">
-        <v>0.0006263175819922929</v>
+        <v>0.000627063191495185</v>
       </c>
       <c r="D3">
-        <v>-2.631758199229299E-05</v>
+        <v>-2.579878910079604E-05</v>
       </c>
       <c r="E3">
-        <v>-4.201954846705363</v>
+        <v>-4.114224762464652</v>
       </c>
     </row>
     <row r="4">
@@ -425,16 +425,16 @@
         <v>1952</v>
       </c>
       <c r="B4">
-        <v>0.0007808219178082191</v>
+        <v>0.0007846351628494586</v>
       </c>
       <c r="C4">
-        <v>0.0008923839315153625</v>
+        <v>0.0008931911211859473</v>
       </c>
       <c r="D4">
-        <v>-0.0001115620137071434</v>
+        <v>-0.0001085559583364887</v>
       </c>
       <c r="E4">
-        <v>-12.501571326783</v>
+        <v>-12.1537211646654</v>
       </c>
     </row>
     <row r="5">
@@ -442,16 +442,16 @@
         <v>1953</v>
       </c>
       <c r="B5">
-        <v>0.0006705479452054794</v>
+        <v>0.0006722818491672769</v>
       </c>
       <c r="C5">
-        <v>0.0007942874899860171</v>
+        <v>0.000791887790619394</v>
       </c>
       <c r="D5">
-        <v>-0.0001237395447805377</v>
+        <v>-0.0001196059414521171</v>
       </c>
       <c r="E5">
-        <v>-15.57868483900157</v>
+        <v>-15.10390018244433</v>
       </c>
     </row>
     <row r="6">
@@ -459,16 +459,16 @@
         <v>1954</v>
       </c>
       <c r="B6">
-        <v>0.0009657534246575343</v>
+        <v>0.000967773776393036</v>
       </c>
       <c r="C6">
-        <v>0.000771937696102794</v>
+        <v>0.0007679984217938117</v>
       </c>
       <c r="D6">
-        <v>0.0001938157285547403</v>
+        <v>0.0001997753545992244</v>
       </c>
       <c r="E6">
-        <v>25.10769062493497</v>
+        <v>26.01246941792011</v>
       </c>
     </row>
     <row r="7">
@@ -476,16 +476,16 @@
         <v>1955</v>
       </c>
       <c r="B7">
-        <v>0.0008356164383561644</v>
+        <v>0.0008382239729680177</v>
       </c>
       <c r="C7">
-        <v>0.000730069559387689</v>
+        <v>0.0007304512196825599</v>
       </c>
       <c r="D7">
-        <v>0.0001055468789684754</v>
+        <v>0.0001077727532854578</v>
       </c>
       <c r="E7">
-        <v>14.4570989998539</v>
+        <v>14.75427111098449</v>
       </c>
     </row>
     <row r="8">
@@ -493,16 +493,16 @@
         <v>1956</v>
       </c>
       <c r="B8">
-        <v>0.0006438356164383561</v>
+        <v>0.0006449791045540373</v>
       </c>
       <c r="C8">
-        <v>0.000691737594888436</v>
+        <v>0.0006927901053026486</v>
       </c>
       <c r="D8">
-        <v>-4.79019784500799E-05</v>
+        <v>-4.781100074861138E-05</v>
       </c>
       <c r="E8">
-        <v>-6.92487712162089</v>
+        <v>-6.901224538668162</v>
       </c>
     </row>
     <row r="9">
@@ -510,16 +510,16 @@
         <v>1957</v>
       </c>
       <c r="B9">
-        <v>0.0008013698630136986</v>
+        <v>0.0008024510361586724</v>
       </c>
       <c r="C9">
-        <v>0.0007274244506685696</v>
+        <v>0.0007246144091458981</v>
       </c>
       <c r="D9">
-        <v>7.394541234512903E-05</v>
+        <v>7.783662701277435E-05</v>
       </c>
       <c r="E9">
-        <v>10.16537350059741</v>
+        <v>10.74179950472145</v>
       </c>
     </row>
     <row r="10">
@@ -527,16 +527,16 @@
         <v>1958</v>
       </c>
       <c r="B10">
-        <v>0.0007876712328767123</v>
+        <v>0.0007880953588970963</v>
       </c>
       <c r="C10">
-        <v>0.0006758190227017959</v>
+        <v>0.0006780310475795056</v>
       </c>
       <c r="D10">
-        <v>0.0001118522101749164</v>
+        <v>0.0001100643113175907</v>
       </c>
       <c r="E10">
-        <v>16.55061583317861</v>
+        <v>16.23293088281251</v>
       </c>
     </row>
     <row r="11">
@@ -544,16 +544,16 @@
         <v>1959</v>
       </c>
       <c r="B11">
-        <v>0.0005897260273972603</v>
+        <v>0.0005910850529475994</v>
       </c>
       <c r="C11">
-        <v>0.000674477699957615</v>
+        <v>0.0006765453124102442</v>
       </c>
       <c r="D11">
-        <v>-8.475167256035473E-05</v>
+        <v>-8.546025946264482E-05</v>
       </c>
       <c r="E11">
-        <v>-12.5655262680561</v>
+        <v>-12.63186040831266</v>
       </c>
     </row>
     <row r="12">
@@ -561,16 +561,16 @@
         <v>1960</v>
       </c>
       <c r="B12">
-        <v>0.0009041095890410959</v>
+        <v>0.0009027991600581399</v>
       </c>
       <c r="C12">
-        <v>0.0007211106247710544</v>
+        <v>0.0007228149721855</v>
       </c>
       <c r="D12">
-        <v>0.0001829989642700415</v>
+        <v>0.00017998418787264</v>
       </c>
       <c r="E12">
-        <v>25.37737733765078</v>
+        <v>24.90045098657</v>
       </c>
     </row>
     <row r="13">
@@ -578,16 +578,16 @@
         <v>1961</v>
       </c>
       <c r="B13">
-        <v>0.0004068493150684931</v>
+        <v>0.0004079966728743662</v>
       </c>
       <c r="C13">
-        <v>0.0008335033986010543</v>
+        <v>0.0008349996183463913</v>
       </c>
       <c r="D13">
-        <v>-0.0004266540835325612</v>
+        <v>-0.0004270029454720252</v>
       </c>
       <c r="E13">
-        <v>-51.18804365388961</v>
+        <v>-51.13810067574034</v>
       </c>
     </row>
     <row r="14">
@@ -595,16 +595,16 @@
         <v>1962</v>
       </c>
       <c r="B14">
-        <v>0.0008013698630136986</v>
+        <v>0.0008004313946064571</v>
       </c>
       <c r="C14">
-        <v>0.0008998041012909868</v>
+        <v>0.0009027422056870041</v>
       </c>
       <c r="D14">
-        <v>-9.84342382772882E-05</v>
+        <v>-0.000102310811080547</v>
       </c>
       <c r="E14">
-        <v>-10.93951873925229</v>
+        <v>-11.33333640944443</v>
       </c>
     </row>
     <row r="15">
@@ -612,16 +612,16 @@
         <v>1963</v>
       </c>
       <c r="B15">
-        <v>0.0009863013698630137</v>
+        <v>0.000987215592526939</v>
       </c>
       <c r="C15">
-        <v>0.0009199818290152927</v>
+        <v>0.0009160703567418131</v>
       </c>
       <c r="D15">
-        <v>6.631954084772101E-05</v>
+        <v>7.11452357851259E-05</v>
       </c>
       <c r="E15">
-        <v>7.208788125598793</v>
+        <v>7.766350615051897</v>
       </c>
     </row>
     <row r="16">
@@ -629,16 +629,16 @@
         <v>1964</v>
       </c>
       <c r="B16">
-        <v>0.0009315068493150684</v>
+        <v>0.0009362134403533977</v>
       </c>
       <c r="C16">
-        <v>0.0008322966531176416</v>
+        <v>0.0008356614550759429</v>
       </c>
       <c r="D16">
-        <v>9.921019619742676E-05</v>
+        <v>0.0001005519852774548</v>
       </c>
       <c r="E16">
-        <v>11.92005228253679</v>
+        <v>12.0326221422187</v>
       </c>
     </row>
     <row r="17">
@@ -646,16 +646,16 @@
         <v>1965</v>
       </c>
       <c r="B17">
-        <v>0.0006465753424657534</v>
+        <v>0.0006482096531711096</v>
       </c>
       <c r="C17">
-        <v>0.0008193529899688895</v>
+        <v>0.0008238603662480223</v>
       </c>
       <c r="D17">
-        <v>-0.0001727776475031361</v>
+        <v>-0.0001756507130769127</v>
       </c>
       <c r="E17">
-        <v>-21.0870832984568</v>
+        <v>-21.32044704090465</v>
       </c>
     </row>
     <row r="18">
@@ -663,16 +663,16 @@
         <v>1966</v>
       </c>
       <c r="B18">
-        <v>0.0009246575342465753</v>
+        <v>0.0009283755558689517</v>
       </c>
       <c r="C18">
-        <v>0.0008154449710428521</v>
+        <v>0.0008204446770942129</v>
       </c>
       <c r="D18">
-        <v>0.0001092125632037233</v>
+        <v>0.0001079308787747389</v>
       </c>
       <c r="E18">
-        <v>13.39300223582887</v>
+        <v>13.15516838466185</v>
       </c>
     </row>
     <row r="19">
@@ -680,16 +680,16 @@
         <v>1967</v>
       </c>
       <c r="B19">
-        <v>0.0006917808219178081</v>
+        <v>0.0006951670355747701</v>
       </c>
       <c r="C19">
-        <v>0.0008201274664704773</v>
+        <v>0.0008241478649637247</v>
       </c>
       <c r="D19">
-        <v>-0.0001283466445526692</v>
+        <v>-0.0001289808293889545</v>
       </c>
       <c r="E19">
-        <v>-15.64959714189616</v>
+        <v>-15.65020488096899</v>
       </c>
     </row>
     <row r="20">
@@ -697,16 +697,16 @@
         <v>1968</v>
       </c>
       <c r="B20">
-        <v>0.001143835616438356</v>
+        <v>0.00114463838799432</v>
       </c>
       <c r="C20">
-        <v>0.0008395577848907317</v>
+        <v>0.0008443703624994693</v>
       </c>
       <c r="D20">
-        <v>0.0003042778315476243</v>
+        <v>0.0003002680254948506</v>
       </c>
       <c r="E20">
-        <v>36.24263118318009</v>
+        <v>35.56117538351417</v>
       </c>
     </row>
     <row r="21">
@@ -714,16 +714,16 @@
         <v>1969</v>
       </c>
       <c r="B21">
-        <v>0.000726027397260274</v>
+        <v>0.0007279888169643569</v>
       </c>
       <c r="C21">
-        <v>0.0007398200405655411</v>
+        <v>0.0007448072869582574</v>
       </c>
       <c r="D21">
-        <v>-1.379264330526712E-05</v>
+        <v>-1.68184699939005E-05</v>
       </c>
       <c r="E21">
-        <v>-1.864324098969204</v>
+        <v>-2.258096864570968</v>
       </c>
     </row>
     <row r="22">
@@ -731,16 +731,16 @@
         <v>1970</v>
       </c>
       <c r="B22">
-        <v>0.001465753424657534</v>
+        <v>0.001468158884709429</v>
       </c>
       <c r="C22">
-        <v>0.00090172460491925</v>
+        <v>0.000906489334248344</v>
       </c>
       <c r="D22">
-        <v>0.0005640288197382841</v>
+        <v>0.0005616695504610852</v>
       </c>
       <c r="E22">
-        <v>62.55000880105664</v>
+        <v>61.96096625084051</v>
       </c>
     </row>
     <row r="23">
@@ -748,16 +748,16 @@
         <v>1971</v>
       </c>
       <c r="B23">
-        <v>0.0008561643835616438</v>
+        <v>0.0008588278038813216</v>
       </c>
       <c r="C23">
-        <v>0.0007793672482678669</v>
+        <v>0.000781286742138817</v>
       </c>
       <c r="D23">
-        <v>7.679713529377692E-05</v>
+        <v>7.754106174250454E-05</v>
       </c>
       <c r="E23">
-        <v>9.853780161336969</v>
+        <v>9.924789140825743</v>
       </c>
     </row>
     <row r="24">
@@ -765,16 +765,16 @@
         <v>1972</v>
       </c>
       <c r="B24">
-        <v>0.0007602739726027397</v>
+        <v>0.0007637643751805284</v>
       </c>
       <c r="C24">
-        <v>0.0007598628740436307</v>
+        <v>0.000761260970554102</v>
       </c>
       <c r="D24">
-        <v>4.110985591089739E-07</v>
+        <v>2.503404626426385E-06</v>
       </c>
       <c r="E24">
-        <v>0.05410167717779155</v>
+        <v>0.3288497273943025</v>
       </c>
     </row>
     <row r="25">
@@ -782,16 +782,16 @@
         <v>1973</v>
       </c>
       <c r="B25">
-        <v>0.0007397260273972603</v>
+        <v>0.0007418358803387</v>
       </c>
       <c r="C25">
-        <v>0.0007075152070758455</v>
+        <v>0.0007093154867970007</v>
       </c>
       <c r="D25">
-        <v>3.221082032141471E-05</v>
+        <v>3.25203935416993E-05</v>
       </c>
       <c r="E25">
-        <v>4.55266826766053</v>
+        <v>4.584757297285169</v>
       </c>
     </row>
     <row r="26">
@@ -799,16 +799,16 @@
         <v>1974</v>
       </c>
       <c r="B26">
-        <v>0.0006917808219178081</v>
+        <v>0.0006960284420504502</v>
       </c>
       <c r="C26">
-        <v>0.0007020765676696391</v>
+        <v>0.0007052047778734456</v>
       </c>
       <c r="D26">
-        <v>-1.029574575183096E-05</v>
+        <v>-9.176335822995451E-06</v>
       </c>
       <c r="E26">
-        <v>-1.466470499934931</v>
+        <v>-1.301229956306708</v>
       </c>
     </row>
     <row r="27">
@@ -816,16 +816,16 @@
         <v>1975</v>
       </c>
       <c r="B27">
-        <v>0.001321917808219178</v>
+        <v>0.001324589309874286</v>
       </c>
       <c r="C27">
-        <v>0.0005576893312991875</v>
+        <v>0.000561669393294361</v>
       </c>
       <c r="D27">
-        <v>0.0007642284769199906</v>
+        <v>0.0007629199165799246</v>
       </c>
       <c r="E27">
-        <v>137.034803075693</v>
+        <v>135.8307797590979</v>
       </c>
     </row>
     <row r="28">
@@ -833,16 +833,16 @@
         <v>1976</v>
       </c>
       <c r="B28">
-        <v>0.0009657534246575343</v>
+        <v>0.000966460634461957</v>
       </c>
       <c r="C28">
-        <v>0.000524900343380629</v>
+        <v>0.0005304555112997982</v>
       </c>
       <c r="D28">
-        <v>0.0004408530812769053</v>
+        <v>0.0004360051231621588</v>
       </c>
       <c r="E28">
-        <v>83.98795825462487</v>
+        <v>82.19447510193579</v>
       </c>
     </row>
     <row r="29">
@@ -850,16 +850,16 @@
         <v>1977</v>
       </c>
       <c r="B29">
-        <v>0.0006061643835616438</v>
+        <v>0.0006072604742501553</v>
       </c>
       <c r="C29">
-        <v>0.0005670352422419017</v>
+        <v>0.0005693355273063846</v>
       </c>
       <c r="D29">
-        <v>3.912914131974209E-05</v>
+        <v>3.792494694377074E-05</v>
       </c>
       <c r="E29">
-        <v>6.900654210668848</v>
+        <v>6.661264777063816</v>
       </c>
     </row>
     <row r="30">
@@ -867,16 +867,16 @@
         <v>1978</v>
       </c>
       <c r="B30">
-        <v>0.001698630136986301</v>
+        <v>0.00170425790228867</v>
       </c>
       <c r="C30">
-        <v>0.0005544906501543809</v>
+        <v>0.0005572543324498991</v>
       </c>
       <c r="D30">
-        <v>0.00114413948683192</v>
+        <v>0.001147003569838771</v>
       </c>
       <c r="E30">
-        <v>206.340627477374</v>
+        <v>205.8312520956299</v>
       </c>
     </row>
     <row r="31">
@@ -884,16 +884,16 @@
         <v>1979</v>
       </c>
       <c r="B31">
-        <v>0.000545890410958904</v>
+        <v>0.0005472440355566978</v>
       </c>
       <c r="C31">
-        <v>0.0005625630461304184</v>
+        <v>0.0005671026534339646</v>
       </c>
       <c r="D31">
-        <v>-1.667263517151436E-05</v>
+        <v>-1.985861787726681E-05</v>
       </c>
       <c r="E31">
-        <v>-2.963691853952519</v>
+        <v>-3.501767758802986</v>
       </c>
     </row>
     <row r="32">
@@ -901,16 +901,16 @@
         <v>1980</v>
       </c>
       <c r="B32">
-        <v>0.0008013698630136986</v>
+        <v>0.0008034864918550222</v>
       </c>
       <c r="C32">
-        <v>0.0005821966587467784</v>
+        <v>0.0005845454966190236</v>
       </c>
       <c r="D32">
-        <v>0.0002191732042669202</v>
+        <v>0.0002189409952359986</v>
       </c>
       <c r="E32">
-        <v>37.64590554997462</v>
+        <v>37.45491095258458</v>
       </c>
     </row>
     <row r="33">
@@ -918,16 +918,16 @@
         <v>1981</v>
       </c>
       <c r="B33">
-        <v>0.0009657534246575343</v>
+        <v>0.0009658822789605574</v>
       </c>
       <c r="C33">
-        <v>0.0005173213286502557</v>
+        <v>0.0005220404921168515</v>
       </c>
       <c r="D33">
-        <v>0.0004484320960072785</v>
+        <v>0.0004438417868437059</v>
       </c>
       <c r="E33">
-        <v>86.68347334088926</v>
+        <v>85.02056709125125</v>
       </c>
     </row>
     <row r="34">
@@ -935,16 +935,16 @@
         <v>1982</v>
       </c>
       <c r="B34">
-        <v>0.0009246575342465753</v>
+        <v>0.0009285557013845663</v>
       </c>
       <c r="C34">
-        <v>0.0005711440274245241</v>
+        <v>0.0005739332455868139</v>
       </c>
       <c r="D34">
-        <v>0.0003535135068220512</v>
+        <v>0.0003546224557977524</v>
       </c>
       <c r="E34">
-        <v>61.89568477432209</v>
+        <v>61.7881014080603</v>
       </c>
     </row>
     <row r="35">
@@ -952,16 +952,16 @@
         <v>1983</v>
       </c>
       <c r="B35">
-        <v>0.00113013698630137</v>
+        <v>0.001135396282932322</v>
       </c>
       <c r="C35">
-        <v>0.0005366941341999198</v>
+        <v>0.0005412699448266396</v>
       </c>
       <c r="D35">
-        <v>0.0005934428521014499</v>
+        <v>0.0005941263381056824</v>
       </c>
       <c r="E35">
-        <v>110.5737540780334</v>
+        <v>109.765255541017</v>
       </c>
     </row>
     <row r="36">
@@ -969,16 +969,169 @@
         <v>1984</v>
       </c>
       <c r="B36">
-        <v>0.001198630136986301</v>
+        <v>0.001203020044235418</v>
       </c>
       <c r="C36">
-        <v>0.0006030896908607315</v>
+        <v>0.0006052224710459337</v>
       </c>
       <c r="D36">
-        <v>0.00059554044612557</v>
+        <v>0.0005977975731894848</v>
       </c>
       <c r="E36">
-        <v>98.74823847106602</v>
+        <v>98.77319527749567</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1985</v>
+      </c>
+      <c r="B37">
+        <v>0.001642536207973294</v>
+      </c>
+      <c r="C37">
+        <v>0.0005517181496719676</v>
+      </c>
+      <c r="D37">
+        <v>0.001090818058301326</v>
+      </c>
+      <c r="E37">
+        <v>197.7129189876912</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1986</v>
+      </c>
+      <c r="B38">
+        <v>0.002803928189882721</v>
+      </c>
+      <c r="C38">
+        <v>0.0005808021220458065</v>
+      </c>
+      <c r="D38">
+        <v>0.002223126067836915</v>
+      </c>
+      <c r="E38">
+        <v>382.768241274019</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>1987</v>
+      </c>
+      <c r="B39">
+        <v>0.004427640502177702</v>
+      </c>
+      <c r="C39">
+        <v>0.0005982112621777112</v>
+      </c>
+      <c r="D39">
+        <v>0.003829429239999991</v>
+      </c>
+      <c r="E39">
+        <v>640.1466308172544</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>1988</v>
+      </c>
+      <c r="B40">
+        <v>0.002771119637453164</v>
+      </c>
+      <c r="C40">
+        <v>0.0006376563521224442</v>
+      </c>
+      <c r="D40">
+        <v>0.002133463285330719</v>
+      </c>
+      <c r="E40">
+        <v>334.5788492860567</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>1989</v>
+      </c>
+      <c r="B41">
+        <v>0.00258858437422026</v>
+      </c>
+      <c r="C41">
+        <v>0.0006198402327631501</v>
+      </c>
+      <c r="D41">
+        <v>0.00196874414145711</v>
+      </c>
+      <c r="E41">
+        <v>317.6212251793916</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>1990</v>
+      </c>
+      <c r="B42">
+        <v>0.002405775996973834</v>
+      </c>
+      <c r="C42">
+        <v>0.0007125047513895942</v>
+      </c>
+      <c r="D42">
+        <v>0.00169327124558424</v>
+      </c>
+      <c r="E42">
+        <v>237.6505198431115</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1991</v>
+      </c>
+      <c r="B43">
+        <v>0.002350898856844621</v>
+      </c>
+      <c r="C43">
+        <v>0.000683549701533608</v>
+      </c>
+      <c r="D43">
+        <v>0.001667349155311013</v>
+      </c>
+      <c r="E43">
+        <v>243.9250798544946</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>1992</v>
+      </c>
+      <c r="B44">
+        <v>0.003673850458044975</v>
+      </c>
+      <c r="C44">
+        <v>0.0006804840453675745</v>
+      </c>
+      <c r="D44">
+        <v>0.0029933664126774</v>
+      </c>
+      <c r="E44">
+        <v>439.8878170700512</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>1993</v>
+      </c>
+      <c r="B45">
+        <v>0.003637478255442569</v>
+      </c>
+      <c r="C45">
+        <v>0.0006582782055514399</v>
+      </c>
+      <c r="D45">
+        <v>0.002979200049891129</v>
+      </c>
+      <c r="E45">
+        <v>452.5746143145439</v>
       </c>
     </row>
   </sheetData>
@@ -1010,7 +1163,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.7203592070082526</v>
+        <v>0.7178305075916765</v>
       </c>
     </row>
     <row r="3">
@@ -1020,7 +1173,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.193769018145775</v>
+        <v>0.2079534677299417</v>
       </c>
     </row>
     <row r="4">
@@ -1030,7 +1183,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.06117333192170868</v>
+        <v>0.04896103743376408</v>
       </c>
     </row>
     <row r="5">
@@ -1040,7 +1193,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.001632834164987429</v>
+        <v>0.001700488736188302</v>
       </c>
     </row>
     <row r="6">
@@ -1050,27 +1203,27 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.001310465008614093</v>
+        <v>0.001271777345492917</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Oswald Spengler</t>
+          <t>Ferdinand Tönnies</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.00118566769592234</v>
+        <v>0.001177789332290973</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ferdinand Tönnies</t>
+          <t>Oswald Spengler</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.001109968704501404</v>
+        <v>0.001104825668031557</v>
       </c>
     </row>
     <row r="9">
@@ -1080,7 +1233,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.0009520960461137551</v>
+        <v>0.001016791226052054</v>
       </c>
     </row>
     <row r="10">
@@ -1090,147 +1243,147 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.0009137439875261031</v>
+        <v>0.0009533979903682305</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Leo Strauss</t>
+          <t>Ludwig Büchner</t>
         </is>
       </c>
       <c r="B11">
-        <v>0.0008739659027596914</v>
+        <v>0.000838451047642363</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ludwig Büchner</t>
+          <t>Heinrich Rickert</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.0007899750892397825</v>
+        <v>0.0008327348971323525</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Heinrich Rickert</t>
+          <t>Külpe</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.0007885133890709877</v>
+        <v>0.000813969421532098</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Külpe</t>
+          <t>Bernard Bolzano</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.0007645659095091974</v>
+        <v>0.0006683850776028619</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bernard Bolzano</t>
+          <t>E T A Hoffmann</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.0006287782683499696</v>
+        <v>0.0006359615773241531</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E T A Hoffmann</t>
+          <t>Hermann Lotze</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.0006004362262466551</v>
+        <v>0.0006211664396287085</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hermann Lotze</t>
+          <t>Theodor Fontane</t>
         </is>
       </c>
       <c r="B17">
-        <v>0.0005807071897192817</v>
+        <v>0.0005885735364440862</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Theodor Fontane</t>
+          <t>Eduard Zeller</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.0005513200303165783</v>
+        <v>0.0005814823055442248</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Eduard Zeller</t>
+          <t>Friedrich Carl von Savigny</t>
         </is>
       </c>
       <c r="B19">
-        <v>0.000541983632182217</v>
+        <v>0.0005589649100600589</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Friedrich Carl von Savigny</t>
+          <t>Barthold Georg Niebuhr</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.0005213274411375762</v>
+        <v>0.0005330814725911656</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Barthold Georg Niebuhr</t>
+          <t>Eduard von Hartmann</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.0005006454763098152</v>
+        <v>0.0005308399025839782</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Eduard von Hartmann</t>
+          <t>Gustav Freytag</t>
         </is>
       </c>
       <c r="B22">
-        <v>0.0004938200544153903</v>
+        <v>0.0004827628148557239</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Gustav Freytag</t>
+          <t>Friedrich Heinrich Jacobi</t>
         </is>
       </c>
       <c r="B23">
-        <v>0.0004527461775851132</v>
+        <v>0.0004549944585398569</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Friedrich Heinrich Jacobi</t>
+          <t>Leo Strauss</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.0004155705612416117</v>
+        <v>0.0004545873280430762</v>
       </c>
     </row>
     <row r="25">
@@ -1240,7 +1393,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.0004058479101155934</v>
+        <v>0.0004446647505705959</v>
       </c>
     </row>
     <row r="26">
@@ -1250,27 +1403,27 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.0003961030144848905</v>
+        <v>0.0004161750296164898</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hans Kelsen</t>
+          <t>Hermann Cohen</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.0003942639778497409</v>
+        <v>0.000407993765611933</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hermann Cohen</t>
+          <t>Eduard Bernstein</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.0003852716833737122</v>
+        <v>0.000386556196554645</v>
       </c>
     </row>
     <row r="29">
@@ -1280,37 +1433,37 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.000350467748741964</v>
+        <v>0.000382392071365237</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Eduard Bernstein</t>
+          <t>Franz Brentano</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.0003465869691902791</v>
+        <v>0.0003563570335364718</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Franz Brentano</t>
+          <t>Ferdinand Lassalle</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.0003352305514484203</v>
+        <v>0.0002911145796534369</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ferdinand Lassalle</t>
+          <t>Hans Kelsen</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.0002655202897360738</v>
+        <v>0.0002349331665981764</v>
       </c>
     </row>
     <row r="33">
@@ -1320,7 +1473,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.0002110361787095155</v>
+        <v>0.0002287536911417351</v>
       </c>
     </row>
     <row r="34">
@@ -1330,7 +1483,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.0002056106642017312</v>
+        <v>0.0002237911927574573</v>
       </c>
     </row>
     <row r="35">
@@ -1340,7 +1493,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.0001833597995725253</v>
+        <v>0.0001983011183257053</v>
       </c>
     </row>
     <row r="36">
@@ -1350,7 +1503,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.0001500337602505386</v>
+        <v>0.0001682037745952988</v>
       </c>
     </row>
     <row r="37">
@@ -1360,7 +1513,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.0001457644804083179</v>
+        <v>0.0001578838369536347</v>
       </c>
     </row>
     <row r="38">
@@ -1370,17 +1523,17 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.0001275865117546344</v>
+        <v>0.0001578034118298331</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Thünen</t>
+          <t>Wundt</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.000120633183720831</v>
+        <v>0.0001329170225077247</v>
       </c>
     </row>
     <row r="40">
@@ -1390,117 +1543,117 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.0001182390968878116</v>
+        <v>0.000128424759721791</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wundt</t>
+          <t>Thünen</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.0001146031874901479</v>
+        <v>0.0001257645951070323</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Max Weber</t>
+          <t>Sombart</t>
         </is>
       </c>
       <c r="B42">
-        <v>9.799538417832561E-05</v>
+        <v>0.0001074558580907064</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Friedrich Schiller</t>
+          <t>Max Weber</t>
         </is>
       </c>
       <c r="B43">
-        <v>9.698484964417792E-05</v>
+        <v>0.0001045226772807926</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Rodbertus</t>
+          <t>Friedrich Schiller</t>
         </is>
       </c>
       <c r="B44">
-        <v>9.078294495364682E-05</v>
+        <v>0.0001021352709773841</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sombart</t>
+          <t>Rodbertus</t>
         </is>
       </c>
       <c r="B45">
-        <v>8.611292997468694E-05</v>
+        <v>9.4578978842939E-05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Windelband</t>
+          <t>Ranke</t>
         </is>
       </c>
       <c r="B46">
-        <v>8.074093569796907E-05</v>
+        <v>9.053387470343176E-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ranke</t>
+          <t>Clausewitz</t>
         </is>
       </c>
       <c r="B47">
-        <v>7.625176187843476E-05</v>
+        <v>8.521545355382399E-05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Martin Luther</t>
+          <t>Windelband</t>
         </is>
       </c>
       <c r="B48">
-        <v>7.302866957280155E-05</v>
+        <v>8.344358616672214E-05</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Clausewitz</t>
+          <t>Martin Luther</t>
         </is>
       </c>
       <c r="B49">
-        <v>7.155309299056343E-05</v>
+        <v>8.290770901780017E-05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ernst Cassirer</t>
+          <t>Schmoller</t>
         </is>
       </c>
       <c r="B50">
-        <v>6.869615616318349E-05</v>
+        <v>7.958123122220722E-05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Schmoller</t>
+          <t>Ernst Cassirer</t>
         </is>
       </c>
       <c r="B51">
-        <v>6.714976394152497E-05</v>
+        <v>7.225522199201743E-05</v>
       </c>
     </row>
     <row r="52">
@@ -1510,37 +1663,37 @@
         </is>
       </c>
       <c r="B52">
-        <v>5.424181518207195E-05</v>
+        <v>5.897020500747577E-05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Karl Jaspers</t>
+          <t>Hamann</t>
         </is>
       </c>
       <c r="B53">
-        <v>5.292577523088616E-05</v>
+        <v>5.694986495607625E-05</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ebbinghaus</t>
+          <t>Karl Jaspers</t>
         </is>
       </c>
       <c r="B54">
-        <v>4.879543598009973E-05</v>
+        <v>5.303221030376909E-05</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hamann</t>
+          <t>Ebbinghaus</t>
         </is>
       </c>
       <c r="B55">
-        <v>4.685763603750767E-05</v>
+        <v>5.134740026143735E-05</v>
       </c>
     </row>
     <row r="56">
@@ -1550,7 +1703,7 @@
         </is>
       </c>
       <c r="B56">
-        <v>4.24872090904536E-05</v>
+        <v>4.990239881907073E-05</v>
       </c>
     </row>
     <row r="57">
@@ -1560,7 +1713,7 @@
         </is>
       </c>
       <c r="B57">
-        <v>4.236581557623622E-05</v>
+        <v>4.461731741463738E-05</v>
       </c>
     </row>
     <row r="58">
@@ -1570,97 +1723,97 @@
         </is>
       </c>
       <c r="B58">
-        <v>3.946130945482881E-05</v>
+        <v>4.047276516002828E-05</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Benjamin Franklin</t>
+          <t>Hölderlin</t>
         </is>
       </c>
       <c r="B59">
-        <v>3.836323157687566E-05</v>
+        <v>4.044520901892982E-05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Hölderlin</t>
+          <t>Schleiermacher</t>
         </is>
       </c>
       <c r="B60">
-        <v>3.727079830135318E-05</v>
+        <v>3.903930434737219E-05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Benjamin Franklin</t>
         </is>
       </c>
       <c r="B61">
-        <v>3.709997696199126E-05</v>
+        <v>3.902085950395544E-05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Walt Whitman</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="B62">
-        <v>3.580091192827379E-05</v>
+        <v>3.780693274461403E-05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Schleiermacher</t>
+          <t>Dilthey</t>
         </is>
       </c>
       <c r="B63">
-        <v>3.572538869612421E-05</v>
+        <v>3.609547634154975E-05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Bentham</t>
+          <t>Walt Whitman</t>
         </is>
       </c>
       <c r="B64">
-        <v>3.450110647320752E-05</v>
+        <v>3.60261191164951E-05</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Frege</t>
+          <t>Bentham</t>
         </is>
       </c>
       <c r="B65">
-        <v>3.44555402755307E-05</v>
+        <v>3.495171924911275E-05</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Thoreau</t>
+          <t>Frege</t>
         </is>
       </c>
       <c r="B66">
-        <v>3.430213960531662E-05</v>
+        <v>3.482891513209224E-05</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Dilthey</t>
+          <t>Thoreau</t>
         </is>
       </c>
       <c r="B67">
-        <v>3.422447281437148E-05</v>
+        <v>3.469542252223806E-05</v>
       </c>
     </row>
     <row r="68">
@@ -1670,47 +1823,47 @@
         </is>
       </c>
       <c r="B68">
-        <v>3.376832748832416E-05</v>
+        <v>3.427716134554335E-05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Malthus</t>
+          <t>Spinoza</t>
         </is>
       </c>
       <c r="B69">
-        <v>3.355744949641884E-05</v>
+        <v>3.378523950082979E-05</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Copernicus</t>
         </is>
       </c>
       <c r="B70">
-        <v>3.343351576079878E-05</v>
+        <v>3.378208580355238E-05</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Adam Smith</t>
+          <t>Malthus</t>
         </is>
       </c>
       <c r="B71">
-        <v>3.330132453452284E-05</v>
+        <v>3.377451525924646E-05</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Copernicus</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B72">
-        <v>3.326936914480454E-05</v>
+        <v>3.370738049622717E-05</v>
       </c>
     </row>
     <row r="73">
@@ -1720,37 +1873,37 @@
         </is>
       </c>
       <c r="B73">
-        <v>3.32201197076954E-05</v>
+        <v>3.368468584385762E-05</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Durkheim</t>
+          <t>Rousseau</t>
         </is>
       </c>
       <c r="B74">
-        <v>3.321326830774857E-05</v>
+        <v>3.367693869506126E-05</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Spinoza</t>
+          <t>Adam Smith</t>
         </is>
       </c>
       <c r="B75">
-        <v>3.309466700284712E-05</v>
+        <v>3.350826971188938E-05</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Rousseau</t>
+          <t>Durkheim</t>
         </is>
       </c>
       <c r="B76">
-        <v>3.255565638286674E-05</v>
+        <v>3.334984948391531E-05</v>
       </c>
     </row>
     <row r="77">
@@ -1760,7 +1913,7 @@
         </is>
       </c>
       <c r="B77">
-        <v>3.245071078084683E-05</v>
+        <v>3.305503579995641E-05</v>
       </c>
     </row>
     <row r="78">
@@ -1770,97 +1923,97 @@
         </is>
       </c>
       <c r="B78">
-        <v>3.22680066692847E-05</v>
+        <v>3.280051413384074E-05</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>William Penn</t>
+          <t>Scheler</t>
         </is>
       </c>
       <c r="B79">
-        <v>3.215035221435993E-05</v>
+        <v>3.254103320011782E-05</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Scheler</t>
+          <t>William Penn</t>
         </is>
       </c>
       <c r="B80">
-        <v>3.208463265095652E-05</v>
+        <v>3.236794967668272E-05</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Lord Byron</t>
+          <t>Aquinas</t>
         </is>
       </c>
       <c r="B81">
-        <v>3.172639435780174E-05</v>
+        <v>3.226949015930386E-05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Oscar Wilde</t>
+          <t>Tocqueville</t>
         </is>
       </c>
       <c r="B82">
-        <v>3.170949054394676E-05</v>
+        <v>3.185928311273643E-05</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Tocqueville</t>
+          <t>Lord Byron</t>
         </is>
       </c>
       <c r="B83">
-        <v>3.160235678894001E-05</v>
+        <v>3.171120762587856E-05</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alexander Hamilton</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="B84">
-        <v>3.142401574805468E-05</v>
+        <v>3.161004777353607E-05</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bakunin</t>
+          <t>Oscar Wilde</t>
         </is>
       </c>
       <c r="B85">
-        <v>3.131473241265709E-05</v>
+        <v>3.160303808767801E-05</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Bakunin</t>
         </is>
       </c>
       <c r="B86">
-        <v>3.12727569996026E-05</v>
+        <v>3.158435209272215E-05</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Aquinas</t>
+          <t>Alexander Hamilton</t>
         </is>
       </c>
       <c r="B87">
-        <v>3.115087643322985E-05</v>
+        <v>3.147896791042047E-05</v>
       </c>
     </row>
     <row r="88">
@@ -1870,77 +2023,77 @@
         </is>
       </c>
       <c r="B88">
-        <v>3.085279930187649E-05</v>
+        <v>3.082687784590839E-05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>John Stuart Mill</t>
+          <t>Montaigne</t>
         </is>
       </c>
       <c r="B89">
-        <v>3.026220513829738E-05</v>
+        <v>3.058531605434363E-05</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Montaigne</t>
+          <t>Hobbes</t>
         </is>
       </c>
       <c r="B90">
-        <v>3.014499712719348E-05</v>
+        <v>3.031724963957126E-05</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Hobbes</t>
+          <t>Descartes</t>
         </is>
       </c>
       <c r="B91">
-        <v>3.000594447486821E-05</v>
+        <v>3.024215045355413E-05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Thomas More</t>
+          <t>John Stuart Mill</t>
         </is>
       </c>
       <c r="B92">
-        <v>2.975792611284773E-05</v>
+        <v>3.015786742344087E-05</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Machiavelli</t>
+          <t>Thomas More</t>
         </is>
       </c>
       <c r="B93">
-        <v>2.96093755829106E-05</v>
+        <v>3.011389872102103E-05</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Samuel Johnson</t>
+          <t>Machiavelli</t>
         </is>
       </c>
       <c r="B94">
-        <v>2.945645708621718E-05</v>
+        <v>2.998067913661334E-05</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Descartes</t>
+          <t>Victor Hugo</t>
         </is>
       </c>
       <c r="B95">
-        <v>2.940493597383382E-05</v>
+        <v>2.949312017470148E-05</v>
       </c>
     </row>
     <row r="96">
@@ -1950,27 +2103,27 @@
         </is>
       </c>
       <c r="B96">
-        <v>2.936990720774349E-05</v>
+        <v>2.944097464219428E-05</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Henry George</t>
+          <t>Samuel Johnson</t>
         </is>
       </c>
       <c r="B97">
-        <v>2.932214059789056E-05</v>
+        <v>2.943030646017535E-05</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Victor Hugo</t>
+          <t>Henry George</t>
         </is>
       </c>
       <c r="B98">
-        <v>2.931302415726067E-05</v>
+        <v>2.920935084590785E-05</v>
       </c>
     </row>
     <row r="99">
@@ -1980,17 +2133,17 @@
         </is>
       </c>
       <c r="B99">
-        <v>2.875182374123958E-05</v>
+        <v>2.860737630884237E-05</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Herbert Spencer</t>
+          <t>Hume</t>
         </is>
       </c>
       <c r="B100">
-        <v>2.804945084096296E-05</v>
+        <v>2.812069833033612E-05</v>
       </c>
     </row>
     <row r="101">
@@ -2000,57 +2153,57 @@
         </is>
       </c>
       <c r="B101">
-        <v>2.782257065333416E-05</v>
+        <v>2.792685317683867E-05</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Proudhon</t>
+          <t>Herbert Spencer</t>
         </is>
       </c>
       <c r="B102">
-        <v>2.765527098483752E-05</v>
+        <v>2.789695595151857E-05</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Robert Browning</t>
+          <t>Faraday</t>
         </is>
       </c>
       <c r="B103">
-        <v>2.754798202120502E-05</v>
+        <v>2.779318378529459E-05</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Hume</t>
+          <t>Proudhon</t>
         </is>
       </c>
       <c r="B104">
-        <v>2.740319701870149E-05</v>
+        <v>2.773908906499412E-05</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Francis Bacon</t>
+          <t>Robert Browning</t>
         </is>
       </c>
       <c r="B105">
-        <v>2.729235014788865E-05</v>
+        <v>2.74334686315264E-05</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Faraday</t>
+          <t>Francis Bacon</t>
         </is>
       </c>
       <c r="B106">
-        <v>2.726295461822307E-05</v>
+        <v>2.73468452127869E-05</v>
       </c>
     </row>
     <row r="107">
@@ -2060,7 +2213,7 @@
         </is>
       </c>
       <c r="B107">
-        <v>2.699633400732105E-05</v>
+        <v>2.684794711814616E-05</v>
       </c>
     </row>
     <row r="108">
@@ -2070,7 +2223,7 @@
         </is>
       </c>
       <c r="B108">
-        <v>2.682213777171906E-05</v>
+        <v>2.669201554688123E-05</v>
       </c>
     </row>
     <row r="109">
@@ -2080,7 +2233,7 @@
         </is>
       </c>
       <c r="B109">
-        <v>2.652968202303041E-05</v>
+        <v>2.650528773585452E-05</v>
       </c>
     </row>
     <row r="110">
@@ -2090,57 +2243,57 @@
         </is>
       </c>
       <c r="B110">
-        <v>2.629015581017431E-05</v>
+        <v>2.628353714188976E-05</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Izaak Walton</t>
         </is>
       </c>
       <c r="B111">
-        <v>2.625320829154504E-05</v>
+        <v>2.621991363043982E-05</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Izaak Walton</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="B112">
-        <v>2.620538916019398E-05</v>
+        <v>2.620396378898151E-05</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Frederick Douglass</t>
+          <t>Dryden</t>
         </is>
       </c>
       <c r="B113">
-        <v>2.602588927473161E-05</v>
+        <v>2.605121329398812E-05</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Ralph Waldo Emerson</t>
+          <t>Frederick Douglass</t>
         </is>
       </c>
       <c r="B114">
-        <v>2.598033471987586E-05</v>
+        <v>2.583888438329996E-05</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Robert Owen</t>
+          <t>Ralph Waldo Emerson</t>
         </is>
       </c>
       <c r="B115">
-        <v>2.579644110934891E-05</v>
+        <v>2.582807620230991E-05</v>
       </c>
     </row>
     <row r="116">
@@ -2150,437 +2303,437 @@
         </is>
       </c>
       <c r="B116">
-        <v>2.556245031981284E-05</v>
+        <v>2.5780181420902E-05</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Talcott Parsons</t>
+          <t>Augustine</t>
         </is>
       </c>
       <c r="B117">
-        <v>2.541965474855452E-05</v>
+        <v>2.56621520939772E-05</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Robert Burns</t>
+          <t>Robert Owen</t>
         </is>
       </c>
       <c r="B118">
-        <v>2.540289781850424E-05</v>
+        <v>2.565003915008277E-05</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Dryden</t>
+          <t>Robert Burns</t>
         </is>
       </c>
       <c r="B119">
-        <v>2.525697787796951E-05</v>
+        <v>2.529687470772111E-05</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Walter Raleigh</t>
+          <t>Voltaire</t>
         </is>
       </c>
       <c r="B120">
-        <v>2.509122672926608E-05</v>
+        <v>2.525480978518576E-05</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Malory</t>
+          <t>Talcott Parsons</t>
         </is>
       </c>
       <c r="B121">
-        <v>2.503347262337445E-05</v>
+        <v>2.514182886428406E-05</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Kropotkin</t>
+          <t>Walter Raleigh</t>
         </is>
       </c>
       <c r="B122">
-        <v>2.497831106712748E-05</v>
+        <v>2.511428138403093E-05</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Cellini</t>
+          <t>Malory</t>
         </is>
       </c>
       <c r="B123">
-        <v>2.483338865380807E-05</v>
+        <v>2.507076717196189E-05</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Voltaire</t>
+          <t>Cellini</t>
         </is>
       </c>
       <c r="B124">
-        <v>2.471651482728082E-05</v>
+        <v>2.501541870662182E-05</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Alexander Pope</t>
+          <t>Kropotkin</t>
         </is>
       </c>
       <c r="B125">
-        <v>2.449718349509394E-05</v>
+        <v>2.497569153125656E-05</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Thomas Carlyle</t>
+          <t>Alexander Pope</t>
         </is>
       </c>
       <c r="B126">
-        <v>2.414004529612308E-05</v>
+        <v>2.442409145026537E-05</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>John Ruskin</t>
+          <t>Thomas Carlyle</t>
         </is>
       </c>
       <c r="B127">
-        <v>2.391305889789038E-05</v>
+        <v>2.396824644415189E-05</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>John Knox</t>
+          <t>Plutarch</t>
         </is>
       </c>
       <c r="B128">
-        <v>2.369441963572722E-05</v>
+        <v>2.381388940933952E-05</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Jonathan Swift</t>
+          <t>John Ruskin</t>
         </is>
       </c>
       <c r="B129">
-        <v>2.366317177323801E-05</v>
+        <v>2.372960476037863E-05</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Hans Christian Andersen</t>
+          <t>John Knox</t>
         </is>
       </c>
       <c r="B130">
-        <v>2.355938950056942E-05</v>
+        <v>2.372506395564194E-05</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Augustine</t>
+          <t>Jonathan Swift</t>
         </is>
       </c>
       <c r="B131">
-        <v>2.35507275889559E-05</v>
+        <v>2.35628312839704E-05</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Plutarch</t>
+          <t>Hans Christian Andersen</t>
         </is>
       </c>
       <c r="B132">
-        <v>2.282033970183616E-05</v>
+        <v>2.341347605334608E-05</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Froissart</t>
+          <t>Cicero</t>
         </is>
       </c>
       <c r="B133">
-        <v>2.27822299663906E-05</v>
+        <v>2.334115447780823E-05</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Tacitus</t>
         </is>
       </c>
       <c r="B134">
-        <v>2.242995761904539E-05</v>
+        <v>2.328120709752643E-05</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Blanqui</t>
+          <t>Herodotus</t>
         </is>
       </c>
       <c r="B135">
-        <v>2.242339213867691E-05</v>
+        <v>2.301881816474803E-05</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>William Wordsworth</t>
+          <t>Froissart</t>
         </is>
       </c>
       <c r="B136">
-        <v>2.241403658536047E-05</v>
+        <v>2.301682002164737E-05</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Tacitus</t>
+          <t>Sophocles</t>
         </is>
       </c>
       <c r="B137">
-        <v>2.240961850186717E-05</v>
+        <v>2.291978502712249E-05</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Thomas Browne</t>
+          <t>Euripides</t>
         </is>
       </c>
       <c r="B138">
-        <v>2.22882601968141E-05</v>
+        <v>2.288924033608705E-05</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Wollstonecraft</t>
+          <t>Blanqui</t>
         </is>
       </c>
       <c r="B139">
-        <v>2.224205573599248E-05</v>
+        <v>2.241289877278967E-05</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Herodotus</t>
+          <t>William Wordsworth</t>
         </is>
       </c>
       <c r="B140">
-        <v>2.200977935860956E-05</v>
+        <v>2.227154508565264E-05</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sophocles</t>
+          <t>Thomas Browne</t>
         </is>
       </c>
       <c r="B141">
-        <v>2.194938007349963E-05</v>
+        <v>2.224765031473916E-05</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Euripides</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="B142">
-        <v>2.189874679131351E-05</v>
+        <v>2.224095030988808E-05</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Auguste Comte</t>
+          <t>Pericles</t>
         </is>
       </c>
       <c r="B143">
-        <v>2.176220830156848E-05</v>
+        <v>2.216651691952132E-05</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sismondi</t>
+          <t>Chaucer</t>
         </is>
       </c>
       <c r="B144">
-        <v>2.170164428727434E-05</v>
+        <v>2.21533305997408E-05</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Cicero</t>
+          <t>Virgil</t>
         </is>
       </c>
       <c r="B145">
-        <v>2.144556132123299E-05</v>
+        <v>2.209359287211045E-05</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>John Calvin</t>
+          <t>Wollstonecraft</t>
         </is>
       </c>
       <c r="B146">
-        <v>2.140766099423472E-05</v>
+        <v>2.209347238783319E-05</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Pericles</t>
+          <t>Aristophanes</t>
         </is>
       </c>
       <c r="B147">
-        <v>2.12971767767235E-05</v>
+        <v>2.18924129126444E-05</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Chaucer</t>
+          <t>Thucydides</t>
         </is>
       </c>
       <c r="B148">
-        <v>2.128917620825376E-05</v>
+        <v>2.185259915075666E-05</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Oliver Goldsmith</t>
+          <t>Aeschylus</t>
         </is>
       </c>
       <c r="B149">
-        <v>2.108722152318667E-05</v>
+        <v>2.176794044754617E-05</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Thucydides</t>
+          <t>Auguste Comte</t>
         </is>
       </c>
       <c r="B150">
-        <v>2.105192811671057E-05</v>
+        <v>2.17312383776352E-05</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Aristophanes</t>
+          <t>Sismondi</t>
         </is>
       </c>
       <c r="B151">
-        <v>2.10497436050398E-05</v>
+        <v>2.168840013538748E-05</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Henry Fielding</t>
+          <t>John Calvin</t>
         </is>
       </c>
       <c r="B152">
-        <v>2.093512089549621E-05</v>
+        <v>2.150622099440657E-05</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Raymond Aron</t>
+          <t>Oliver Goldsmith</t>
         </is>
       </c>
       <c r="B153">
-        <v>2.092417960620664E-05</v>
+        <v>2.096345650272465E-05</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Aeschylus</t>
+          <t>Henry Fielding</t>
         </is>
       </c>
       <c r="B154">
-        <v>2.091896756989472E-05</v>
+        <v>2.082328883843494E-05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>William Harvey</t>
+          <t>Raymond Aron</t>
         </is>
       </c>
       <c r="B155">
-        <v>2.062465265856226E-05</v>
+        <v>2.080093023716319E-05</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>John Bunyan</t>
+          <t>William Harvey</t>
         </is>
       </c>
       <c r="B156">
-        <v>2.057835410091356E-05</v>
+        <v>2.065503013133509E-05</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>William Godwin</t>
+          <t>John Bunyan</t>
         </is>
       </c>
       <c r="B157">
-        <v>2.046040394328054E-05</v>
+        <v>2.051673688324039E-05</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Virgil</t>
+          <t>William Godwin</t>
         </is>
       </c>
       <c r="B158">
-        <v>2.04300898906648E-05</v>
+        <v>2.031399439368245E-05</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Edward Bellamy</t>
+          <t>Hippocrates</t>
         </is>
       </c>
       <c r="B159">
-        <v>2.036902263076382E-05</v>
+        <v>2.022330060955145E-05</v>
       </c>
     </row>
     <row r="160">
@@ -2590,17 +2743,17 @@
         </is>
       </c>
       <c r="B160">
-        <v>2.035375111959676E-05</v>
+        <v>2.020154245895468E-05</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>William Graham Sumner</t>
+          <t>Edward Bellamy</t>
         </is>
       </c>
       <c r="B161">
-        <v>2.019514625763281E-05</v>
+        <v>2.017772265694179E-05</v>
       </c>
     </row>
     <row r="162">
@@ -2610,127 +2763,127 @@
         </is>
       </c>
       <c r="B162">
-        <v>2.018808954942394E-05</v>
+        <v>2.016131194176105E-05</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>John Woolman</t>
+          <t>William Graham Sumner</t>
         </is>
       </c>
       <c r="B163">
-        <v>2.008408969228621E-05</v>
+        <v>2.000580738790554E-05</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Carl Friedrich</t>
+          <t>John Woolman</t>
         </is>
       </c>
       <c r="B164">
-        <v>2.00433182765358E-05</v>
+        <v>1.996732875159728E-05</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Isaiah Berlin</t>
+          <t>Carl Friedrich</t>
         </is>
       </c>
       <c r="B165">
-        <v>1.996184893839823E-05</v>
+        <v>1.980971697237337E-05</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Percy Bysshe Shelley</t>
+          <t>Isaiah Berlin</t>
         </is>
       </c>
       <c r="B166">
-        <v>1.986979782678304E-05</v>
+        <v>1.972162669685505E-05</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Bastiat</t>
+          <t>Percy Bysshe Shelley</t>
         </is>
       </c>
       <c r="B167">
-        <v>1.978099386634965E-05</v>
+        <v>1.972041335498183E-05</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Benjamin Constant</t>
+          <t>Bastiat</t>
         </is>
       </c>
       <c r="B168">
-        <v>1.97469981113824E-05</v>
+        <v>1.970927519248804E-05</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Richard Cobden</t>
+          <t>Benjamin Constant</t>
         </is>
       </c>
       <c r="B169">
-        <v>1.964876525546766E-05</v>
+        <v>1.969415730605452E-05</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Hippocrates</t>
+          <t>Marcus Aurelius</t>
         </is>
       </c>
       <c r="B170">
-        <v>1.948587450254265E-05</v>
+        <v>1.964724056533653E-05</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>William Harrison</t>
+          <t>Kempis</t>
         </is>
       </c>
       <c r="B171">
-        <v>1.946059834197196E-05</v>
+        <v>1.950381067999581E-05</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Kempis</t>
+          <t>Richard Cobden</t>
         </is>
       </c>
       <c r="B172">
-        <v>1.9382278841773E-05</v>
+        <v>1.948831673637333E-05</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Vilfredo Pareto</t>
+          <t>William Harrison</t>
         </is>
       </c>
       <c r="B173">
-        <v>1.936001925104207E-05</v>
+        <v>1.945656514154118E-05</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Marcus Aurelius</t>
+          <t>Vilfredo Pareto</t>
         </is>
       </c>
       <c r="B174">
-        <v>1.91064889798674E-05</v>
+        <v>1.922957566923447E-05</v>
       </c>
     </row>
     <row r="175">
@@ -2740,27 +2893,27 @@
         </is>
       </c>
       <c r="B175">
-        <v>1.903663668283061E-05</v>
+        <v>1.882123851891965E-05</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>John Rawls</t>
+          <t>Charles Fourier</t>
         </is>
       </c>
       <c r="B176">
-        <v>1.875805172517369E-05</v>
+        <v>1.866160542133307E-05</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Charles Fourier</t>
+          <t>John Rawls</t>
         </is>
       </c>
       <c r="B177">
-        <v>1.873024458162222E-05</v>
+        <v>1.852754270752067E-05</v>
       </c>
     </row>
     <row r="178">
@@ -2770,7 +2923,7 @@
         </is>
       </c>
       <c r="B178">
-        <v>1.858567242006307E-05</v>
+        <v>1.846155404829037E-05</v>
       </c>
     </row>
     <row r="179">
@@ -2780,47 +2933,47 @@
         </is>
       </c>
       <c r="B179">
-        <v>1.857567720401451E-05</v>
+        <v>1.842907805399395E-05</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Joseph Lister</t>
+          <t>Dante Alighieri</t>
         </is>
       </c>
       <c r="B180">
-        <v>1.849166064804871E-05</v>
+        <v>1.834002070173221E-05</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Gaetano Mosca</t>
+          <t>Joseph Lister</t>
         </is>
       </c>
       <c r="B181">
-        <v>1.844972595785926E-05</v>
+        <v>1.833774655521074E-05</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>James Fitzjames Stephen</t>
+          <t>Gaetano Mosca</t>
         </is>
       </c>
       <c r="B182">
-        <v>1.842379855919826E-05</v>
+        <v>1.832976287786812E-05</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Julius Evola</t>
+          <t>James Fitzjames Stephen</t>
         </is>
       </c>
       <c r="B183">
-        <v>1.835921242256615E-05</v>
+        <v>1.825944390467656E-05</v>
       </c>
     </row>
     <row r="184">
@@ -2830,97 +2983,97 @@
         </is>
       </c>
       <c r="B184">
-        <v>1.832440939438953E-05</v>
+        <v>1.815839295578514E-05</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Quentin Skinner</t>
+          <t>Julius Evola</t>
         </is>
       </c>
       <c r="B185">
-        <v>1.830569777097629E-05</v>
+        <v>1.815601627021528E-05</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Robert Nozick</t>
+          <t>Quentin Skinner</t>
         </is>
       </c>
       <c r="B186">
-        <v>1.827719039942529E-05</v>
+        <v>1.807702200088741E-05</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Dante Alighieri</t>
+          <t>Hippolyte Taine</t>
         </is>
       </c>
       <c r="B187">
-        <v>1.820556713191067E-05</v>
+        <v>1.8052367042977E-05</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Hippolyte Taine</t>
+          <t>Robert Nozick</t>
         </is>
       </c>
       <c r="B188">
-        <v>1.814093618027318E-05</v>
+        <v>1.805138573549974E-05</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Lujo Brentano</t>
+          <t>Alessandro Manzoni</t>
         </is>
       </c>
       <c r="B189">
-        <v>1.812399534598228E-05</v>
+        <v>1.800542374954457E-05</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Auberon Herbert</t>
+          <t>Lujo Brentano</t>
         </is>
       </c>
       <c r="B190">
-        <v>1.810250820685699E-05</v>
+        <v>1.795748060407992E-05</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Alessandro Manzoni</t>
+          <t>Auberon Herbert</t>
         </is>
       </c>
       <c r="B191">
-        <v>1.807684341052397E-05</v>
+        <v>1.792844147313586E-05</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Archibald Geikie</t>
+          <t>William Caxton</t>
         </is>
       </c>
       <c r="B192">
-        <v>1.790008029363813E-05</v>
+        <v>1.789404795980114E-05</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>William Caxton</t>
+          <t>Archibald Geikie</t>
         </is>
       </c>
       <c r="B193">
-        <v>1.787028379565072E-05</v>
+        <v>1.774075764628931E-05</v>
       </c>
     </row>
     <row r="194">
@@ -2930,27 +3083,27 @@
         </is>
       </c>
       <c r="B194">
-        <v>1.786505478947717E-05</v>
+        <v>1.771198068294E-05</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Otto Pfleiderer</t>
+          <t>Jean Racine</t>
         </is>
       </c>
       <c r="B195">
-        <v>1.76774887821315E-05</v>
+        <v>1.766349549732345E-05</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Jean Racine</t>
+          <t>Pierre Corneille</t>
         </is>
       </c>
       <c r="B196">
-        <v>1.766833013395489E-05</v>
+        <v>1.76228463735873E-05</v>
       </c>
     </row>
     <row r="197">
@@ -2960,117 +3113,117 @@
         </is>
       </c>
       <c r="B197">
-        <v>1.76153310283474E-05</v>
+        <v>1.753030531881805E-05</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Pierre Corneille</t>
+          <t>Otto Pfleiderer</t>
         </is>
       </c>
       <c r="B198">
-        <v>1.761331612771072E-05</v>
+        <v>1.751674785235411E-05</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>de Gouges</t>
+          <t>Aesop</t>
         </is>
       </c>
       <c r="B199">
-        <v>1.737715818944469E-05</v>
+        <v>1.731744014204199E-05</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>William Roper</t>
+          <t>de Gouges</t>
         </is>
       </c>
       <c r="B200">
-        <v>1.729679946355846E-05</v>
+        <v>1.729228346337636E-05</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Philip Nichols</t>
+          <t>William Roper</t>
         </is>
       </c>
       <c r="B201">
-        <v>1.700067664737891E-05</v>
+        <v>1.725974684527578E-05</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Ambroise Paré</t>
+          <t>Philip Nichols</t>
         </is>
       </c>
       <c r="B202">
-        <v>1.683907849883813E-05</v>
+        <v>1.696396429487267E-05</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Bigges</t>
+          <t>Ambroise Paré</t>
         </is>
       </c>
       <c r="B203">
-        <v>1.682014247695895E-05</v>
+        <v>1.685754246132099E-05</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Pedro Calderón de la Barca</t>
+          <t>Bigges</t>
         </is>
       </c>
       <c r="B204">
-        <v>1.678706527261588E-05</v>
+        <v>1.680122453844712E-05</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Aesop</t>
+          <t>Pedro Calderón de la Barca</t>
         </is>
       </c>
       <c r="B205">
-        <v>1.671390832066701E-05</v>
+        <v>1.679301335974709E-05</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Francis Pretty</t>
+          <t>Epictetus</t>
         </is>
       </c>
       <c r="B206">
-        <v>1.662302550080338E-05</v>
+        <v>1.671095563899901E-05</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Edward Haies</t>
+          <t>Francis Pretty</t>
         </is>
       </c>
       <c r="B207">
-        <v>1.659506393968886E-05</v>
+        <v>1.660625369322385E-05</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Epictetus</t>
+          <t>Edward Haies</t>
         </is>
       </c>
       <c r="B208">
-        <v>1.62930342653874E-05</v>
+        <v>1.657706397710338E-05</v>
       </c>
     </row>
     <row r="209">
@@ -3080,7 +3233,7 @@
         </is>
       </c>
       <c r="B209">
-        <v>1.277864205999922E-05</v>
+        <v>1.431153707668402E-05</v>
       </c>
     </row>
     <row r="210">
@@ -3090,7 +3243,7 @@
         </is>
       </c>
       <c r="B210">
-        <v>1.224281568928956E-05</v>
+        <v>1.254147718062521E-05</v>
       </c>
     </row>
     <row r="211">
@@ -3100,7 +3253,7 @@
         </is>
       </c>
       <c r="B211">
-        <v>8.65255579176229E-06</v>
+        <v>9.567503401364771E-06</v>
       </c>
     </row>
     <row r="212">
@@ -3110,7 +3263,7 @@
         </is>
       </c>
       <c r="B212">
-        <v>6.656387675397186E-06</v>
+        <v>7.328033497003629E-06</v>
       </c>
     </row>
     <row r="213">
@@ -3120,7 +3273,7 @@
         </is>
       </c>
       <c r="B213">
-        <v>1.389074462647907E-06</v>
+        <v>1.40069684567937E-06</v>
       </c>
     </row>
   </sheetData>
@@ -3152,7 +3305,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.009192685645617661</v>
+        <v>0.008218513443565705</v>
       </c>
     </row>
     <row r="3">
@@ -3312,7 +3465,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>5.313016371548262E-05</v>
+        <v>0.0005863465732004154</v>
       </c>
     </row>
     <row r="19">
@@ -3472,7 +3625,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.02442979849782768</v>
+        <v>0.02436435390561018</v>
       </c>
     </row>
     <row r="35">
@@ -3632,7 +3785,7 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.00110953897232784</v>
+        <v>0.0005734481333797273</v>
       </c>
     </row>
     <row r="51">
@@ -3792,7 +3945,7 @@
         </is>
       </c>
       <c r="B66">
-        <v>0.002407312699818647</v>
+        <v>0.002661284301617034</v>
       </c>
     </row>
     <row r="67">
@@ -3952,7 +4105,7 @@
         </is>
       </c>
       <c r="B82">
-        <v>0.0003384905847239884</v>
+        <v>0.000514662572859221</v>
       </c>
     </row>
     <row r="83">
@@ -4112,7 +4265,7 @@
         </is>
       </c>
       <c r="B98">
-        <v>0.0002872827286974025</v>
+        <v>0.0004865241543915317</v>
       </c>
     </row>
     <row r="99">
@@ -4272,7 +4425,7 @@
         </is>
       </c>
       <c r="B114">
-        <v>7.341347881308324E-05</v>
+        <v>0.0007701206865490208</v>
       </c>
     </row>
     <row r="115">
@@ -4432,7 +4585,7 @@
         </is>
       </c>
       <c r="B130">
-        <v>0.0004513509997097372</v>
+        <v>0.000530384758978102</v>
       </c>
     </row>
     <row r="131">
@@ -4592,7 +4745,7 @@
         </is>
       </c>
       <c r="B146">
-        <v>9.298323172116827E-06</v>
+        <v>7.071230707400629E-06</v>
       </c>
     </row>
     <row r="147">
@@ -4752,7 +4905,7 @@
         </is>
       </c>
       <c r="B162">
-        <v>0.0001302852960543428</v>
+        <v>0.0001221786333355007</v>
       </c>
     </row>
     <row r="163">
@@ -4912,7 +5065,7 @@
         </is>
       </c>
       <c r="B178">
-        <v>0.1602568455531167</v>
+        <v>0.1605422795241316</v>
       </c>
     </row>
     <row r="179">
@@ -5072,7 +5225,7 @@
         </is>
       </c>
       <c r="B194">
-        <v>0.2894013156566584</v>
+        <v>0.2876399675141859</v>
       </c>
     </row>
     <row r="195">
@@ -5232,7 +5385,7 @@
         </is>
       </c>
       <c r="B210">
-        <v>0.1957510352966649</v>
+        <v>0.1967030374599144</v>
       </c>
     </row>
     <row r="211">
@@ -5392,7 +5545,7 @@
         </is>
       </c>
       <c r="B226">
-        <v>0.316108216103082</v>
+        <v>0.3162798271075744</v>
       </c>
     </row>
   </sheetData>
@@ -5432,7 +5585,7 @@
         <v>0.9828230022404779</v>
       </c>
       <c r="C2">
-        <v>0.9803818714576715</v>
+        <v>0.98034086522077</v>
       </c>
     </row>
     <row r="3">
@@ -5445,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.003296130728207154</v>
+        <v>0.002718064884070168</v>
       </c>
     </row>
     <row r="4">
@@ -5458,7 +5611,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0.9964375780482529</v>
+        <v>0.9964084674364283</v>
       </c>
     </row>
     <row r="5">
@@ -5471,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.0006851135978013829</v>
+        <v>0.0006898668842416057</v>
       </c>
     </row>
     <row r="6">
@@ -5484,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.0002726829535892506</v>
+        <v>0.0002854272132987471</v>
       </c>
     </row>
     <row r="7">
@@ -5497,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.0003239236461312817</v>
+        <v>0.0003342132179037147</v>
       </c>
     </row>
     <row r="8">
@@ -5510,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.0001762640396183643</v>
+        <v>0.0001764978717540241</v>
       </c>
     </row>
     <row r="9">
@@ -5523,7 +5676,7 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>5.000718498031128E-05</v>
+        <v>5.047769920360471E-05</v>
       </c>
     </row>
     <row r="10">
@@ -5536,7 +5689,7 @@
         <v>0.9381107491856677</v>
       </c>
       <c r="C10">
-        <v>0.9391746852193816</v>
+        <v>0.9389486608994514</v>
       </c>
     </row>
     <row r="11">
@@ -5549,7 +5702,7 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>0.9765055839840813</v>
+        <v>0.9758679944396842</v>
       </c>
     </row>
     <row r="12">
@@ -5562,7 +5715,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>0.983283661894274</v>
+        <v>0.9824037230934941</v>
       </c>
     </row>
     <row r="13">
@@ -5572,10 +5725,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.0007853881278538813</v>
+        <v>0.00078814268646685</v>
       </c>
       <c r="C13">
-        <v>0.000748915109795782</v>
+        <v>0.0007506210664966398</v>
       </c>
     </row>
     <row r="14">
@@ -5585,10 +5738,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.0007543378995433789</v>
+        <v>0.0007572507482049439</v>
       </c>
       <c r="C14">
-        <v>0.000818308475827406</v>
+        <v>0.000822817636101987</v>
       </c>
     </row>
     <row r="15">
@@ -5598,10 +5751,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.0006335616438356165</v>
+        <v>0.0006339602952933686</v>
       </c>
       <c r="C15">
-        <v>0.0007430305744432412</v>
+        <v>0.0007447866343140452</v>
       </c>
     </row>
     <row r="16">
@@ -5611,10 +5764,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.000823972602739726</v>
+        <v>0.0008260931995094435</v>
       </c>
       <c r="C16">
-        <v>0.0007654315818255009</v>
+        <v>0.0007634458106985886</v>
       </c>
     </row>
   </sheetData>
@@ -5646,7 +5799,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>2.902055526661715</v>
+        <v>9.046552565102733</v>
       </c>
     </row>
     <row r="3">
@@ -5656,7 +5809,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.06310679611650485</v>
+        <v>0.02884615384615385</v>
       </c>
     </row>
     <row r="4">
@@ -5666,7 +5819,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -5698,1847 +5851,1847 @@
         </is>
       </c>
       <c r="B2">
-        <v>31.51269217443135</v>
+        <v>32.42384217269854</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Robert Nozick</t>
+          <t>Otto Pfleiderer</t>
         </is>
       </c>
       <c r="B3">
-        <v>15.04566217902114</v>
+        <v>22.60397962819328</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>John Rawls</t>
+          <t>Robert Nozick</t>
         </is>
       </c>
       <c r="B4">
-        <v>7.018584596858997</v>
+        <v>15.34233944210795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hans Kelsen</t>
+          <t>Carl Stumpf</t>
         </is>
       </c>
       <c r="B5">
-        <v>5.709648588589779</v>
+        <v>10.73103995225579</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Robert Merton</t>
+          <t>John Rawls</t>
         </is>
       </c>
       <c r="B6">
-        <v>5.132570061509233</v>
+        <v>10.34009121890006</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Carl Stumpf</t>
+          <t>Carl Schmitt</t>
         </is>
       </c>
       <c r="B7">
-        <v>4.37157222364657</v>
+        <v>9.046552565102733</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Frege</t>
+          <t>James Fitzjames Stephen</t>
         </is>
       </c>
       <c r="B8">
-        <v>3.916551341976666</v>
+        <v>7.594674645898272</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Clausewitz</t>
+          <t>Hans Kelsen</t>
         </is>
       </c>
       <c r="B9">
-        <v>3.90512693198536</v>
+        <v>7.369798596755571</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Friedrich Schiller</t>
+          <t>Heinrich Rickert</t>
         </is>
       </c>
       <c r="B10">
-        <v>3.646979834127953</v>
+        <v>7.070057531184949</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Wollstonecraft</t>
+          <t>Norbert Elias</t>
         </is>
       </c>
       <c r="B11">
-        <v>3.483602732030084</v>
+        <v>6.800180786581897</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norbert Elias</t>
+          <t>Ferdinand Tönnies</t>
         </is>
       </c>
       <c r="B12">
-        <v>3.311162489616704</v>
+        <v>5.776098339623066</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>William Godwin</t>
+          <t>Ludwig Büchner</t>
         </is>
       </c>
       <c r="B13">
-        <v>3.000293310767172</v>
+        <v>5.726607656672677</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Carl Schmitt</t>
+          <t>Talcott Parsons</t>
         </is>
       </c>
       <c r="B14">
-        <v>2.902055526661715</v>
+        <v>5.496008251558002</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Heinrich Rickert</t>
+          <t>Wollstonecraft</t>
         </is>
       </c>
       <c r="B15">
-        <v>2.717712480154079</v>
+        <v>4.957349323226377</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Homer</t>
+          <t>Clausewitz</t>
         </is>
       </c>
       <c r="B16">
-        <v>2.633462247201431</v>
+        <v>4.512819704410779</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Carl Friedrich</t>
+          <t>Ernst Cassirer</t>
         </is>
       </c>
       <c r="B17">
-        <v>2.556788611064248</v>
+        <v>4.28549256351091</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Voltaire</t>
+          <t>Carl Friedrich</t>
         </is>
       </c>
       <c r="B18">
-        <v>2.460463270567665</v>
+        <v>3.650606191875096</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ernst Cassirer</t>
+          <t>Frege</t>
         </is>
       </c>
       <c r="B19">
-        <v>2.358065199713632</v>
+        <v>3.633906484851046</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Charles Darwin</t>
+          <t>Ralph Waldo Emerson</t>
         </is>
       </c>
       <c r="B20">
-        <v>2.288238526807172</v>
+        <v>3.624603088481728</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hölderlin</t>
+          <t>William Graham Sumner</t>
         </is>
       </c>
       <c r="B21">
-        <v>2.266324566337437</v>
+        <v>3.454531126973381</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Karl Mannheim</t>
+          <t>Sainte Beuve</t>
         </is>
       </c>
       <c r="B22">
-        <v>2.106476145543284</v>
+        <v>3.453765868889749</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>William Graham Sumner</t>
+          <t>Eduard von Hartmann</t>
         </is>
       </c>
       <c r="B23">
-        <v>2.057449492049535</v>
+        <v>3.357472554093437</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lujo Brentano</t>
+          <t>Bernard Bolzano</t>
         </is>
       </c>
       <c r="B24">
-        <v>2.04896291073618</v>
+        <v>3.225260708010795</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ralph Waldo Emerson</t>
+          <t>Robert Merton</t>
         </is>
       </c>
       <c r="B25">
-        <v>2.032137676513555</v>
+        <v>3.107041372302851</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ludwig Büchner</t>
+          <t>William Godwin</t>
         </is>
       </c>
       <c r="B26">
-        <v>2.022632356236663</v>
+        <v>3.008235611882765</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Voltaire</t>
         </is>
       </c>
       <c r="B27">
-        <v>1.936153989508149</v>
+        <v>2.922494806490701</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Eduard Zeller</t>
+          <t>Homer</t>
         </is>
       </c>
       <c r="B28">
-        <v>1.933343313654825</v>
+        <v>2.914623406566164</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Theodor Fontane</t>
+          <t>Lujo Brentano</t>
         </is>
       </c>
       <c r="B29">
-        <v>1.89208477907527</v>
+        <v>2.81540864437794</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cervantes</t>
+          <t>Leo Strauss</t>
         </is>
       </c>
       <c r="B30">
-        <v>1.889939694446827</v>
+        <v>2.60186418729239</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Franz Brentano</t>
+          <t>Friedrich Schiller</t>
         </is>
       </c>
       <c r="B31">
-        <v>1.843963034574126</v>
+        <v>2.445162474874139</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Aesop</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="B32">
-        <v>1.781910006016818</v>
+        <v>2.430242312053801</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Epictetus</t>
+          <t>Hermann Cohen</t>
         </is>
       </c>
       <c r="B33">
-        <v>1.771476227291855</v>
+        <v>2.376433986702201</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Helmholtz</t>
+          <t>Theodor Fontane</t>
         </is>
       </c>
       <c r="B34">
-        <v>1.760358278592068</v>
+        <v>2.354745096915738</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>John Calvin</t>
         </is>
       </c>
       <c r="B35">
-        <v>1.753710135802297</v>
+        <v>2.347166803369488</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Scheler</t>
+          <t>Descartes</t>
         </is>
       </c>
       <c r="B36">
-        <v>1.744882699964837</v>
+        <v>2.312966753905003</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Faraday</t>
         </is>
       </c>
       <c r="B37">
-        <v>1.74163943320687</v>
+        <v>2.254531680137044</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Eduard von Hartmann</t>
+          <t>Külpe</t>
         </is>
       </c>
       <c r="B38">
-        <v>1.740432945287839</v>
+        <v>2.158432267301408</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Durkheim</t>
+          <t>Tocqueville</t>
         </is>
       </c>
       <c r="B39">
-        <v>1.692926287549678</v>
+        <v>2.139553161241265</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Isaiah Berlin</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B40">
-        <v>1.669839141593994</v>
+        <v>2.128124077738723</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Auguste Comte</t>
+          <t>Durkheim</t>
         </is>
       </c>
       <c r="B41">
-        <v>1.658460419554382</v>
+        <v>2.114150863851928</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Walter Raleigh</t>
+          <t>Epictetus</t>
         </is>
       </c>
       <c r="B42">
-        <v>1.627572539866367</v>
+        <v>2.090862050883202</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bernard Bolzano</t>
+          <t>Kempis</t>
         </is>
       </c>
       <c r="B43">
-        <v>1.607235409147058</v>
+        <v>2.079934158761332</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Kempis</t>
+          <t>Hermann Lotze</t>
         </is>
       </c>
       <c r="B44">
-        <v>1.595401462988666</v>
+        <v>2.065494432230034</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Leo Strauss</t>
+          <t>Eduard Zeller</t>
         </is>
       </c>
       <c r="B45">
-        <v>1.590927324617152</v>
+        <v>2.059142626059232</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Descartes</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="B46">
-        <v>1.585265159362174</v>
+        <v>2.045820001383692</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Grimmelshausen</t>
+          <t>John Knox</t>
         </is>
       </c>
       <c r="B47">
-        <v>1.559768542701722</v>
+        <v>2.020396831761911</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Faraday</t>
+          <t>Raymond Aron</t>
         </is>
       </c>
       <c r="B48">
-        <v>1.551502556113356</v>
+        <v>1.975497789474492</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sainte Beuve</t>
+          <t>Scheler</t>
         </is>
       </c>
       <c r="B49">
-        <v>1.535800626929432</v>
+        <v>1.895116244739541</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>William Caxton</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="B50">
-        <v>1.532884082687178</v>
+        <v>1.890819298263044</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Pericles</t>
+          <t>de Gouges</t>
         </is>
       </c>
       <c r="B51">
-        <v>1.504327511484238</v>
+        <v>1.844588647071122</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>William Wordsworth</t>
+          <t>Frederick Douglass</t>
         </is>
       </c>
       <c r="B52">
-        <v>1.50323204093991</v>
+        <v>1.839140349879354</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Victor Hugo</t>
         </is>
       </c>
       <c r="B53">
-        <v>1.490157233417158</v>
+        <v>1.798558499149028</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Molière</t>
+          <t>Richard Cobden</t>
         </is>
       </c>
       <c r="B54">
-        <v>1.465878755953587</v>
+        <v>1.786595338439991</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Euripides</t>
+          <t>Robert Owen</t>
         </is>
       </c>
       <c r="B55">
-        <v>1.461711577162138</v>
+        <v>1.745562947724394</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>John Ruskin</t>
+          <t>Charles Darwin</t>
         </is>
       </c>
       <c r="B56">
-        <v>1.446791968559678</v>
+        <v>1.737639882095797</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>August Bebel</t>
+          <t>Franz Brentano</t>
         </is>
       </c>
       <c r="B57">
-        <v>1.418667742235319</v>
+        <v>1.7293185805705</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Friedrich Heinrich Jacobi</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="B58">
-        <v>1.38792578844645</v>
+        <v>1.715147300277809</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Copernicus</t>
+          <t>William Roper</t>
         </is>
       </c>
       <c r="B59">
-        <v>1.369053956533646</v>
+        <v>1.69747217451968</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jean Racine</t>
+          <t>Karl Jaspers</t>
         </is>
       </c>
       <c r="B60">
-        <v>1.360609705331587</v>
+        <v>1.659850785811777</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Friedrich List</t>
+          <t>Helmholtz</t>
         </is>
       </c>
       <c r="B61">
-        <v>1.359917657346028</v>
+        <v>1.637369583648603</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>James Fitzjames Stephen</t>
+          <t>Pericles</t>
         </is>
       </c>
       <c r="B62">
-        <v>1.352205047622211</v>
+        <v>1.625869133264583</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Abraham Lincoln</t>
+          <t>William Wordsworth</t>
         </is>
       </c>
       <c r="B63">
-        <v>1.345402092147334</v>
+        <v>1.623000517449325</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Richard Cobden</t>
+          <t>Aesop</t>
         </is>
       </c>
       <c r="B64">
-        <v>1.3393603058795</v>
+        <v>1.570761446420206</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Külpe</t>
+          <t>Isaiah Berlin</t>
         </is>
       </c>
       <c r="B65">
-        <v>1.322982363057819</v>
+        <v>1.56551051520362</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Tocqueville</t>
+          <t>August Bebel</t>
         </is>
       </c>
       <c r="B66">
-        <v>1.30896645592091</v>
+        <v>1.564564959160273</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>William Penn</t>
+          <t>Hobbes</t>
         </is>
       </c>
       <c r="B67">
-        <v>1.307400215244674</v>
+        <v>1.560897998124829</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Spinoza</t>
+          <t>Cervantes</t>
         </is>
       </c>
       <c r="B68">
-        <v>1.299558875048536</v>
+        <v>1.552791906702046</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Ferdinand Lassalle</t>
+          <t>Molière</t>
         </is>
       </c>
       <c r="B69">
-        <v>1.256370980948349</v>
+        <v>1.549100879687825</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Oscar Wilde</t>
+          <t>Martin Luther</t>
         </is>
       </c>
       <c r="B70">
-        <v>1.253925842182162</v>
+        <v>1.527527865330944</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Newton</t>
+          <t>Copernicus</t>
         </is>
       </c>
       <c r="B71">
-        <v>1.247107280495272</v>
+        <v>1.517617804403132</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ebbinghaus</t>
+          <t>Ferdinand Lassalle</t>
         </is>
       </c>
       <c r="B72">
-        <v>1.239175789856517</v>
+        <v>1.503677655188218</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Percy Bysshe Shelley</t>
+          <t>Friedrich List</t>
         </is>
       </c>
       <c r="B73">
-        <v>1.221937406070963</v>
+        <v>1.499725939833101</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sophocles</t>
+          <t>Francis Bacon</t>
         </is>
       </c>
       <c r="B74">
-        <v>1.206017652074399</v>
+        <v>1.498804562067316</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Oswald Spengler</t>
+          <t>William Penn</t>
         </is>
       </c>
       <c r="B75">
-        <v>1.202769634019826</v>
+        <v>1.483498006498645</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Karl Jaspers</t>
+          <t>William Harvey</t>
         </is>
       </c>
       <c r="B76">
-        <v>1.192736898452989</v>
+        <v>1.477802445181492</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Vilfredo Pareto</t>
+          <t>Wilhelm von Humboldt</t>
         </is>
       </c>
       <c r="B77">
-        <v>1.182685206003626</v>
+        <v>1.468096073021257</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Otto Pfleiderer</t>
+          <t>Oswald Spengler</t>
         </is>
       </c>
       <c r="B78">
-        <v>1.167094157910542</v>
+        <v>1.465576277264123</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Chaucer</t>
+          <t>Hans Christian Andersen</t>
         </is>
       </c>
       <c r="B79">
-        <v>1.162378334938898</v>
+        <v>1.450175919749271</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Benjamin Franklin</t>
+          <t>Euripides</t>
         </is>
       </c>
       <c r="B80">
-        <v>1.156405849271429</v>
+        <v>1.450092981758738</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Hermann Cohen</t>
+          <t>Grimmelshausen</t>
         </is>
       </c>
       <c r="B81">
-        <v>1.143019880161824</v>
+        <v>1.433070003122191</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Thoreau</t>
+          <t>Dostoyevsky</t>
         </is>
       </c>
       <c r="B82">
-        <v>1.141648565802068</v>
+        <v>1.423605927192864</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Edgar Jung</t>
+          <t>Walter Raleigh</t>
         </is>
       </c>
       <c r="B83">
-        <v>1.14126019138398</v>
+        <v>1.413692886977334</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>John Woolman</t>
+          <t>Oliver Goldsmith</t>
         </is>
       </c>
       <c r="B84">
-        <v>1.136777445211778</v>
+        <v>1.395982099464846</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Hermann Lotze</t>
+          <t>Malthus</t>
         </is>
       </c>
       <c r="B85">
-        <v>1.134694715553776</v>
+        <v>1.393617278685284</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Robert Owen</t>
+          <t>John Woolman</t>
         </is>
       </c>
       <c r="B86">
-        <v>1.129146688197733</v>
+        <v>1.39170407670892</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Vilfredo Pareto</t>
         </is>
       </c>
       <c r="B87">
-        <v>1.128691810026125</v>
+        <v>1.387659888230291</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Goethe</t>
+          <t>Sophocles</t>
         </is>
       </c>
       <c r="B88">
-        <v>1.090972634161</v>
+        <v>1.359615415557016</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Schleiermacher</t>
+          <t>Leibniz</t>
         </is>
       </c>
       <c r="B89">
-        <v>1.077214617993832</v>
+        <v>1.28106623966122</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Nassau Senior</t>
+          <t>Augustine</t>
         </is>
       </c>
       <c r="B90">
-        <v>1.054007946741553</v>
+        <v>1.273182515857248</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Thomas More</t>
+          <t>Thoreau</t>
         </is>
       </c>
       <c r="B91">
-        <v>1.053758801248128</v>
+        <v>1.273158062903212</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Schäffle</t>
+          <t>William Caxton</t>
         </is>
       </c>
       <c r="B92">
-        <v>1.046632103720106</v>
+        <v>1.270497991639419</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Victor Hugo</t>
+          <t>Jean Racine</t>
         </is>
       </c>
       <c r="B93">
-        <v>1.043289111876448</v>
+        <v>1.264257990298704</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Malthus</t>
+          <t>Edmund Burke</t>
         </is>
       </c>
       <c r="B94">
-        <v>1.035273884669023</v>
+        <v>1.257665477477109</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Augustine</t>
+          <t>Karl Mannheim</t>
         </is>
       </c>
       <c r="B95">
-        <v>1.033098052743655</v>
+        <v>1.238619853819108</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Oliver Goldsmith</t>
+          <t>Froissart</t>
         </is>
       </c>
       <c r="B96">
-        <v>1.031389066599416</v>
+        <v>1.227619942908096</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Martin Luther</t>
+          <t>Ebbinghaus</t>
         </is>
       </c>
       <c r="B97">
-        <v>1.014781368919799</v>
+        <v>1.203027432886334</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Dostoyevsky</t>
+          <t>Edmund Spenser</t>
         </is>
       </c>
       <c r="B98">
-        <v>0.9959577653869375</v>
+        <v>1.201870240345255</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Gaetano Mosca</t>
+          <t>Goethe</t>
         </is>
       </c>
       <c r="B99">
-        <v>0.9949495039438054</v>
+        <v>1.201485785017509</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cicero</t>
+          <t>John Ruskin</t>
         </is>
       </c>
       <c r="B100">
-        <v>0.9924674779905525</v>
+        <v>1.181185449254416</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Adam Smith</t>
+          <t>Schäffle</t>
         </is>
       </c>
       <c r="B101">
-        <v>0.9911021646337626</v>
+        <v>1.148387612790605</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Leibniz</t>
+          <t>Jonathan Swift</t>
         </is>
       </c>
       <c r="B102">
-        <v>0.9749405138657223</v>
+        <v>1.140741418974068</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sombart</t>
+          <t>Henry Fielding</t>
         </is>
       </c>
       <c r="B103">
-        <v>0.9671947006042569</v>
+        <v>1.134599901858585</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Plutarch</t>
+          <t>Aquinas</t>
         </is>
       </c>
       <c r="B104">
-        <v>0.9603362049430882</v>
+        <v>1.131884447065087</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Herodotus</t>
+          <t>Percy Bysshe Shelley</t>
         </is>
       </c>
       <c r="B105">
-        <v>0.9603265590229038</v>
+        <v>1.12749848503294</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Wundt</t>
+          <t>Hume</t>
         </is>
       </c>
       <c r="B106">
-        <v>0.9500761072330053</v>
+        <v>1.125581809829899</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Rodbertus</t>
+          <t>Hippolyte Taine</t>
         </is>
       </c>
       <c r="B107">
-        <v>0.9470567443540318</v>
+        <v>1.103837209262035</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Hippolyte Taine</t>
+          <t>Auguste Comte</t>
         </is>
       </c>
       <c r="B108">
-        <v>0.9445337148748948</v>
+        <v>1.101550479510637</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Barthold Georg Niebuhr</t>
+          <t>Auberon Herbert</t>
         </is>
       </c>
       <c r="B109">
-        <v>0.9444381442302319</v>
+        <v>1.098378958415961</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Talcott Parsons</t>
+          <t>Friedrich Heinrich Jacobi</t>
         </is>
       </c>
       <c r="B110">
-        <v>0.9401593020066609</v>
+        <v>1.094510414854861</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Thomas Carlyle</t>
+          <t>Herbart</t>
         </is>
       </c>
       <c r="B111">
-        <v>0.939621979231804</v>
+        <v>1.08781566591199</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ranke</t>
+          <t>Newton</t>
         </is>
       </c>
       <c r="B112">
-        <v>0.9359142712672385</v>
+        <v>1.081563182162457</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Wilhelm von Humboldt</t>
+          <t>Schmoller</t>
         </is>
       </c>
       <c r="B113">
-        <v>0.9307486455856974</v>
+        <v>1.075821949113577</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Friedrich Carl von Savigny</t>
+          <t>Marcus Aurelius</t>
         </is>
       </c>
       <c r="B114">
-        <v>0.9232284812132312</v>
+        <v>1.065334934784887</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Herbart</t>
+          <t>Benjamin Constant</t>
         </is>
       </c>
       <c r="B115">
-        <v>0.9227557782274078</v>
+        <v>1.062895285492435</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Hippocrates</t>
+          <t>Sismondi</t>
         </is>
       </c>
       <c r="B116">
-        <v>0.9174354460428608</v>
+        <v>1.062555244335812</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>William Harrison</t>
+          <t>Charles Fourier</t>
         </is>
       </c>
       <c r="B117">
-        <v>0.9161619453172053</v>
+        <v>1.060456616732184</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Francis Pretty</t>
+          <t>Simmel</t>
         </is>
       </c>
       <c r="B118">
-        <v>0.8989924161076396</v>
+        <v>1.058796188821338</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Izaak Walton</t>
+          <t>Edgar Jung</t>
         </is>
       </c>
       <c r="B119">
-        <v>0.8988650695564157</v>
+        <v>1.056781361139538</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>John Knox</t>
+          <t>Rodbertus</t>
         </is>
       </c>
       <c r="B120">
-        <v>0.891216152636265</v>
+        <v>1.043398172192368</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Schmoller</t>
+          <t>Wundt</t>
         </is>
       </c>
       <c r="B121">
-        <v>0.8842439699786018</v>
+        <v>1.031298855190708</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Frederick Douglass</t>
+          <t>Ernst Jünger</t>
         </is>
       </c>
       <c r="B122">
-        <v>0.8812663237662517</v>
+        <v>1.030233655863491</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Henry Fielding</t>
+          <t>Chaucer</t>
         </is>
       </c>
       <c r="B123">
-        <v>0.8805741386038581</v>
+        <v>1.026637739459022</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Froissart</t>
+          <t>Benjamin Franklin</t>
         </is>
       </c>
       <c r="B124">
-        <v>0.8740198234106763</v>
+        <v>1.015344817258042</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Rousseau</t>
+          <t>E T A Hoffmann</t>
         </is>
       </c>
       <c r="B125">
-        <v>0.8477953620684192</v>
+        <v>1.013352967155909</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Gustav Freytag</t>
+          <t>Oscar Wilde</t>
         </is>
       </c>
       <c r="B126">
-        <v>0.8468598873947357</v>
+        <v>1.010365140127118</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Thomas Mann</t>
+          <t>Barthold Georg Niebuhr</t>
         </is>
       </c>
       <c r="B127">
-        <v>0.8412309326665921</v>
+        <v>0.9974635083480448</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Julius Evola</t>
+          <t>Abraham Lincoln</t>
         </is>
       </c>
       <c r="B128">
-        <v>0.8361366340876472</v>
+        <v>0.9964507236576388</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Bastiat</t>
+          <t>Spinoza</t>
         </is>
       </c>
       <c r="B129">
-        <v>0.8298626020263412</v>
+        <v>0.9954353435581441</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cellini</t>
+          <t>Thomas More</t>
         </is>
       </c>
       <c r="B130">
-        <v>0.8168873620804336</v>
+        <v>0.9929465036209744</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Jonathan Swift</t>
+          <t>Herodotus</t>
         </is>
       </c>
       <c r="B131">
-        <v>0.8168301442352791</v>
+        <v>0.9914696884410553</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Oliver Wendell Holmes</t>
+          <t>Aeschylus</t>
         </is>
       </c>
       <c r="B132">
-        <v>0.815066975175464</v>
+        <v>0.9797239989698218</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Simmel</t>
+          <t>Francis Pretty</t>
         </is>
       </c>
       <c r="B133">
-        <v>0.8135892093132079</v>
+        <v>0.9786517211574808</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ambroise Paré</t>
+          <t>William Harrison</t>
         </is>
       </c>
       <c r="B134">
-        <v>0.7848677434699003</v>
+        <v>0.9756472521624695</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>E T A Hoffmann</t>
+          <t>Thucydides</t>
         </is>
       </c>
       <c r="B135">
-        <v>0.7839174089549678</v>
+        <v>0.9614523424869564</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>John Milton</t>
+          <t>Oliver Wendell Holmes</t>
         </is>
       </c>
       <c r="B136">
-        <v>0.7837708632239085</v>
+        <v>0.9570010328837614</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Aeschylus</t>
+          <t>Dryden</t>
         </is>
       </c>
       <c r="B137">
-        <v>0.7699243692768951</v>
+        <v>0.9556266592592151</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Edmund Spenser</t>
+          <t>Nassau Senior</t>
         </is>
       </c>
       <c r="B138">
-        <v>0.7698278292916164</v>
+        <v>0.9448148047035785</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Alexander Hamilton</t>
+          <t>Aristotle</t>
         </is>
       </c>
       <c r="B139">
-        <v>0.7612122513609797</v>
+        <v>0.9326814450558882</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Dante Alighieri</t>
+          <t>Ambroise Paré</t>
         </is>
       </c>
       <c r="B140">
-        <v>0.7527042245800981</v>
+        <v>0.9206916870413366</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sismondi</t>
+          <t>Schleiermacher</t>
         </is>
       </c>
       <c r="B141">
-        <v>0.7414525924783696</v>
+        <v>0.9162176611390813</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Samuel Johnson</t>
+          <t>Plutarch</t>
         </is>
       </c>
       <c r="B142">
-        <v>0.7388852430346609</v>
+        <v>0.9114874320910573</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Benjamin Constant</t>
+          <t>Gotthold Ephraim Lessing</t>
         </is>
       </c>
       <c r="B143">
-        <v>0.7328261454475496</v>
+        <v>0.9051041766434258</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Max Weber</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="B144">
-        <v>0.7320713420269098</v>
+        <v>0.8971392980399729</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Edward Haies</t>
+          <t>Edward Bellamy</t>
         </is>
       </c>
       <c r="B145">
-        <v>0.7287920090776401</v>
+        <v>0.8932554278454076</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Lord Byron</t>
+          <t>Dilthey</t>
         </is>
       </c>
       <c r="B146">
-        <v>0.7271450188401798</v>
+        <v>0.8914446300907344</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Izaak Walton</t>
         </is>
       </c>
       <c r="B147">
-        <v>0.7258614950109641</v>
+        <v>0.8884187531031034</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Ferdinand Tönnies</t>
+          <t>Thomas Carlyle</t>
         </is>
       </c>
       <c r="B148">
-        <v>0.725119163029734</v>
+        <v>0.8798315482798683</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Pasteur</t>
+          <t>Thomas Mann</t>
         </is>
       </c>
       <c r="B149">
-        <v>0.7184091107549514</v>
+        <v>0.8644315396787478</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Mazzini</t>
+          <t>Dante Alighieri</t>
         </is>
       </c>
       <c r="B150">
-        <v>0.7183902549873998</v>
+        <v>0.8643158491714457</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Pliny the Younger</t>
+          <t>Bastiat</t>
         </is>
       </c>
       <c r="B151">
-        <v>0.7099783757113163</v>
+        <v>0.8586794217040564</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Malory</t>
+          <t>Max Weber</t>
         </is>
       </c>
       <c r="B152">
-        <v>0.6957376730302407</v>
+        <v>0.8535966029250514</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Thünen</t>
+          <t>Virgil</t>
         </is>
       </c>
       <c r="B153">
-        <v>0.6890800343117035</v>
+        <v>0.8389727074371039</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>John Stuart Mill</t>
+          <t>Sombart</t>
         </is>
       </c>
       <c r="B154">
-        <v>0.6819284973431082</v>
+        <v>0.8314167620896401</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Pierre Corneille</t>
+          <t>John Bunyan</t>
         </is>
       </c>
       <c r="B155">
-        <v>0.681008044236082</v>
+        <v>0.8187668979667423</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Marcus Aurelius</t>
+          <t>Rousseau</t>
         </is>
       </c>
       <c r="B156">
-        <v>0.6789631416159911</v>
+        <v>0.8159157611346077</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>William Harvey</t>
+          <t>Cicero</t>
         </is>
       </c>
       <c r="B157">
-        <v>0.6758179571192187</v>
+        <v>0.814648152940405</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Blanqui</t>
+          <t>Ranke</t>
         </is>
       </c>
       <c r="B158">
-        <v>0.6727699929747933</v>
+        <v>0.811861586271783</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Aristophanes</t>
+          <t>Mazzini</t>
         </is>
       </c>
       <c r="B159">
-        <v>0.6638981581683435</v>
+        <v>0.8006225979850176</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Dilthey</t>
+          <t>David Ricardo</t>
         </is>
       </c>
       <c r="B160">
-        <v>0.6613618009530109</v>
+        <v>0.7991075944094445</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>de Gouges</t>
+          <t>Bakunin</t>
         </is>
       </c>
       <c r="B161">
-        <v>0.6594309556735659</v>
+        <v>0.7974415616521467</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Archibald Geikie</t>
         </is>
       </c>
       <c r="B162">
-        <v>0.6515676230269709</v>
+        <v>0.7968534390247208</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Robert Burns</t>
+          <t>Hippocrates</t>
         </is>
       </c>
       <c r="B163">
-        <v>0.6507816333530885</v>
+        <v>0.7901767656857807</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ernst Jünger</t>
+          <t>Alexander Hamilton</t>
         </is>
       </c>
       <c r="B164">
-        <v>0.6473795525286401</v>
+        <v>0.7781786583773171</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>David Ricardo</t>
+          <t>Gaetano Mosca</t>
         </is>
       </c>
       <c r="B165">
-        <v>0.6469436498104761</v>
+        <v>0.7781040336308841</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Virgil</t>
+          <t>Aristophanes</t>
         </is>
       </c>
       <c r="B166">
-        <v>0.6466720661223501</v>
+        <v>0.7688263734684857</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Hume</t>
+          <t>John Milton</t>
         </is>
       </c>
       <c r="B167">
-        <v>0.6461992382073485</v>
+        <v>0.7677435656803833</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Machiavelli</t>
+          <t>John Stuart Mill</t>
         </is>
       </c>
       <c r="B168">
-        <v>0.6403305498005628</v>
+        <v>0.7626669721002257</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Dryden</t>
+          <t>Julius Evola</t>
         </is>
       </c>
       <c r="B169">
-        <v>0.6366189167273938</v>
+        <v>0.7580356021169201</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Alessandro Manzoni</t>
+          <t>Adam Smith</t>
         </is>
       </c>
       <c r="B170">
-        <v>0.627545581088915</v>
+        <v>0.756168971180153</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Charles Fourier</t>
+          <t>Robert Burns</t>
         </is>
       </c>
       <c r="B171">
-        <v>0.6195849491978862</v>
+        <v>0.7556317296432921</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Hamann</t>
+          <t>Thünen</t>
         </is>
       </c>
       <c r="B172">
-        <v>0.6091279334850497</v>
+        <v>0.7554921688534073</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>William Roper</t>
+          <t>Machiavelli</t>
         </is>
       </c>
       <c r="B173">
-        <v>0.5790859065033113</v>
+        <v>0.7456575426656459</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Archibald Geikie</t>
+          <t>Lord Byron</t>
         </is>
       </c>
       <c r="B174">
-        <v>0.5745374229585459</v>
+        <v>0.7436061429197611</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Francis Bacon</t>
+          <t>Friedrich Carl von Savigny</t>
         </is>
       </c>
       <c r="B175">
-        <v>0.5721269036419004</v>
+        <v>0.7264858936175664</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Simon Newcomb</t>
+          <t>Arthur Moeller van den Bruck</t>
         </is>
       </c>
       <c r="B176">
-        <v>0.5582375202795303</v>
+        <v>0.7247618100291777</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Renan</t>
+          <t>Windelband</t>
         </is>
       </c>
       <c r="B177">
-        <v>0.5569100021772292</v>
+        <v>0.722285568957268</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Bakunin</t>
+          <t>Malory</t>
         </is>
       </c>
       <c r="B178">
-        <v>0.5508949039845127</v>
+        <v>0.721924260293541</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Arthur Moeller van den Bruck</t>
+          <t>Gustav Freytag</t>
         </is>
       </c>
       <c r="B179">
-        <v>0.5496549892651815</v>
+        <v>0.7122201390032485</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>John Bunyan</t>
+          <t>Edward Haies</t>
         </is>
       </c>
       <c r="B180">
-        <v>0.5439689905292885</v>
+        <v>0.7032598448394708</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Pedro Calderón de la Barca</t>
+          <t>Cellini</t>
         </is>
       </c>
       <c r="B181">
-        <v>0.5402066258842669</v>
+        <v>0.6960813112909974</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Auberon Herbert</t>
+          <t>Robert Browning</t>
         </is>
       </c>
       <c r="B182">
-        <v>0.5374466919973219</v>
+        <v>0.691545026111809</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Thucydides</t>
+          <t>Pliny the Younger</t>
         </is>
       </c>
       <c r="B183">
-        <v>0.5338727966513414</v>
+        <v>0.6905011560065437</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Joseph Lister</t>
+          <t>Samuel Johnson</t>
         </is>
       </c>
       <c r="B184">
-        <v>0.521579758811089</v>
+        <v>0.6774396012674971</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Gotthold Ephraim Lessing</t>
+          <t>Plato</t>
         </is>
       </c>
       <c r="B185">
-        <v>0.5169776350636269</v>
+        <v>0.6746315055382738</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Eduard Bernstein</t>
+          <t>Pasteur</t>
         </is>
       </c>
       <c r="B186">
-        <v>0.503628182308851</v>
+        <v>0.6616790853834374</v>
       </c>
     </row>
     <row r="187">
@@ -7548,77 +7701,77 @@
         </is>
       </c>
       <c r="B187">
-        <v>0.4987498615331624</v>
+        <v>0.6607738711537975</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Aristotle</t>
+          <t>John C Calhoun</t>
         </is>
       </c>
       <c r="B188">
-        <v>0.4941981210714329</v>
+        <v>0.6545258786243013</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Hobbes</t>
+          <t>Blanqui</t>
         </is>
       </c>
       <c r="B189">
-        <v>0.4940934381601755</v>
+        <v>0.6483289508556732</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Hans Christian Andersen</t>
+          <t>Proudhon</t>
         </is>
       </c>
       <c r="B190">
-        <v>0.4880682639330019</v>
+        <v>0.6388569001830631</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Windelband</t>
+          <t>Kropotkin</t>
         </is>
       </c>
       <c r="B191">
-        <v>0.4789047351078835</v>
+        <v>0.601387440392456</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Aquinas</t>
+          <t>Simon Newcomb</t>
         </is>
       </c>
       <c r="B192">
-        <v>0.4628258722660915</v>
+        <v>0.5994705408716321</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Proudhon</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B193">
-        <v>0.4511902875224399</v>
+        <v>0.5962222201883556</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Robert Browning</t>
+          <t>Hamann</t>
         </is>
       </c>
       <c r="B194">
-        <v>0.4494831912420808</v>
+        <v>0.5888775059078665</v>
       </c>
     </row>
     <row r="195">
@@ -7628,175 +7781,181 @@
         </is>
       </c>
       <c r="B195">
-        <v>0.4362567396191013</v>
+        <v>0.5880611029719498</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Plato</t>
+          <t>Renan</t>
         </is>
       </c>
       <c r="B196">
-        <v>0.4273041575173152</v>
+        <v>0.5637369593285775</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Bentham</t>
+          <t>Eduard Bernstein</t>
         </is>
       </c>
       <c r="B197">
-        <v>0.421461179572914</v>
+        <v>0.5619589972595791</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>John C Calhoun</t>
+          <t>Pierre Corneille</t>
         </is>
       </c>
       <c r="B198">
-        <v>0.4191274226495587</v>
+        <v>0.5577540932340017</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Marlowe</t>
+          <t>Walt Whitman</t>
         </is>
       </c>
       <c r="B199">
-        <v>0.4071794713430137</v>
+        <v>0.5438115797288779</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Tacitus</t>
+          <t>Pedro Calderón de la Barca</t>
         </is>
       </c>
       <c r="B200">
-        <v>0.3767856666448376</v>
+        <v>0.5333304429413268</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Edmund Burke</t>
+          <t>Alessandro Manzoni</t>
         </is>
       </c>
       <c r="B201">
-        <v>0.3213374421182225</v>
+        <v>0.5075022948504553</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Edward Bellamy</t>
+          <t>Marlowe</t>
         </is>
       </c>
       <c r="B202">
-        <v>0.2948695617232696</v>
+        <v>0.5066083101414969</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Edward Jenner</t>
+          <t>Tacitus</t>
         </is>
       </c>
       <c r="B203">
-        <v>0.2812808454411979</v>
+        <v>0.4842173450344132</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Bigges</t>
+          <t>Joseph Lister</t>
         </is>
       </c>
       <c r="B204">
-        <v>0.2626658943034851</v>
+        <v>0.457961423834318</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Philip Nichols</t>
+          <t>Edward Jenner</t>
         </is>
       </c>
       <c r="B205">
-        <v>0.2481650471517837</v>
+        <v>0.4547199976706328</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Herder</t>
+          <t>Bentham</t>
         </is>
       </c>
       <c r="B206">
-        <v>0.2134450929714388</v>
+        <v>0.4467297740664867</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Kropotkin</t>
+          <t>Bigges</t>
         </is>
       </c>
       <c r="B207">
-        <v>0.2030928108408902</v>
+        <v>0.2983095798034047</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Herbert Spencer</t>
-        </is>
+          <t>Philip Nichols</t>
+        </is>
+      </c>
+      <c r="B208">
+        <v>0.2766750484137164</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>John Calvin</t>
-        </is>
+          <t>Herder</t>
+        </is>
+      </c>
+      <c r="B209">
+        <v>0.2479007640844151</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Montaigne</t>
+          <t>Herbert Spencer</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Raymond Aron</t>
+          <t>Hölderlin</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Rilke</t>
+          <t>Montaigne</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Thomas Browne</t>
+          <t>Rilke</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Walt Whitman</t>
+          <t>Thomas Browne</t>
         </is>
       </c>
     </row>
